--- a/data/default/LayerHerd.xlsx
+++ b/data/default/LayerHerd.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnka0003\Documents\#1 Projekt\MISTRA Food Futures WP5\CIBUSmod Food Systems Model\CIBUSmod\data\prod_parameters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnka0003\Git repos\CIBUSmod\data\default\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,6 +14,7 @@
   <sheets>
     <sheet name="default" sheetId="2" r:id="rId1"/>
     <sheet name="Feed rations" sheetId="3" r:id="rId2"/>
+    <sheet name="references" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -62,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="130">
   <si>
     <t>value</t>
   </si>
@@ -199,9 +200,6 @@
     <t>Carlsson et al 2009</t>
   </si>
   <si>
-    <t>Avg gård A and B</t>
-  </si>
-  <si>
     <t>weeks_in_stage</t>
   </si>
   <si>
@@ -217,15 +215,9 @@
     <t>laying hens (&gt;59 weeks)</t>
   </si>
   <si>
-    <t>assumed for now</t>
-  </si>
-  <si>
     <t>???</t>
   </si>
   <si>
-    <t>assumed for now. 2.3% for broilers</t>
-  </si>
-  <si>
     <t>kg/head/year</t>
   </si>
   <si>
@@ -268,9 +260,6 @@
     <t>As fed [%]</t>
   </si>
   <si>
-    <t>Sonesson 2008</t>
-  </si>
-  <si>
     <t>Feed:</t>
   </si>
   <si>
@@ -295,9 +284,6 @@
     <t>Värp 110</t>
   </si>
   <si>
-    <t>Carlsson</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -422,6 +408,51 @@
   </si>
   <si>
     <t>Slaughter and live weights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sonesson, U., Cederberg, C., Flysjö, A. &amp; Carlsson, B. (2008). Livscykelanalys (LCA) av svenska ägg (ver.2). SIK-rapport Nr 783 2008.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carlsson, B., Sonesson, U., Cederberg, C. &amp; Sund, V. (2009). Livscykelanalys (LCA) av svenska ekologiska ägg. SIK-rapport Nr 797 2009.  </t>
+  </si>
+  <si>
+    <t>Sonesson et al (2008)</t>
+  </si>
+  <si>
+    <t>Carlsson et al (2009)</t>
+  </si>
+  <si>
+    <t>Assumed same as for broiler parents</t>
+  </si>
+  <si>
+    <t>Ida Ljungkvist, pers. comm.</t>
+  </si>
+  <si>
+    <t>assumption</t>
+  </si>
+  <si>
+    <t>% of inserted</t>
+  </si>
+  <si>
+    <t>% of slaughtered</t>
+  </si>
+  <si>
+    <t>assumption. 2.3% for broilers</t>
+  </si>
+  <si>
+    <t>Set to reach 5.0% for laying period. Avg gård A and B</t>
+  </si>
+  <si>
+    <t>mortality per stage</t>
+  </si>
+  <si>
+    <t>mortality laying period</t>
+  </si>
+  <si>
+    <t>Calc. mortality per stage</t>
+  </si>
+  <si>
+    <t>Set to reach 10.0% for laying period</t>
   </si>
 </sst>
 </file>
@@ -432,7 +463,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -498,8 +529,14 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -533,6 +570,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -667,7 +710,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -681,7 +724,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -803,6 +845,15 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1084,7 +1135,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H176"/>
+  <dimension ref="A1:Q176"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
@@ -1097,7 +1148,7 @@
     <col min="8" max="8" width="23.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -1123,7 +1174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>13</v>
       </c>
@@ -1135,7 +1186,7 @@
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D3" t="s">
         <v>36</v>
       </c>
@@ -1153,43 +1204,46 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E4" s="13">
+        <v>90</v>
+      </c>
+      <c r="E4" s="12">
         <v>100</v>
       </c>
       <c r="F4" t="s">
         <v>4</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D5" t="s">
-        <v>96</v>
-      </c>
-      <c r="E5" s="11">
+        <v>91</v>
+      </c>
+      <c r="E5" s="78">
         <v>12.5</v>
       </c>
       <c r="F5" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G5" s="79" t="s">
+        <v>119</v>
+      </c>
+      <c r="H5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="E6" s="4"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E7" s="4">
         <f>15-0+1</f>
@@ -1199,12 +1253,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E8" s="4">
         <f>28-16+1</f>
@@ -1214,12 +1268,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E9" s="4">
         <f>59-29+1</f>
@@ -1229,12 +1283,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E10" s="4">
         <f>(E3+E7)-60+1</f>
@@ -1244,50 +1298,76 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="E11" s="4"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="M11" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="11">
-        <v>10</v>
+      <c r="E12" s="78">
+        <v>2</v>
       </c>
       <c r="F12" t="s">
+        <v>122</v>
+      </c>
+      <c r="G12" s="79" t="s">
+        <v>121</v>
+      </c>
+      <c r="M12" s="80" t="s">
+        <v>126</v>
+      </c>
+      <c r="N12" s="81"/>
+      <c r="O12" s="81"/>
+      <c r="P12" s="81">
+        <v>3.45</v>
+      </c>
+      <c r="Q12" s="82" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>42</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="11">
-        <v>10</v>
+      <c r="E13" s="78">
+        <v>2</v>
       </c>
       <c r="F13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G13" s="79" t="s">
+        <v>121</v>
+      </c>
+      <c r="M13" s="83" t="s">
+        <v>127</v>
+      </c>
+      <c r="N13" s="84"/>
+      <c r="O13" s="84"/>
+      <c r="P13" s="85">
+        <f>(1-1*(1-P12/100)*(1-P12/100)*(1-P12/100))*100</f>
+        <v>9.9970313624999978</v>
+      </c>
+      <c r="Q13" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="G13" s="8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -1295,20 +1375,19 @@
         <v>8</v>
       </c>
       <c r="E14" s="4">
-        <f>(3.85+6.24)/2</f>
-        <v>5.0449999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="F14" t="s">
-        <v>6</v>
+        <v>122</v>
       </c>
       <c r="G14" t="s">
-        <v>45</v>
+        <v>125</v>
       </c>
       <c r="H14" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1316,27 +1395,30 @@
         <v>8</v>
       </c>
       <c r="E15" s="4">
-        <v>10</v>
+        <v>3.45</v>
       </c>
       <c r="F15" t="s">
-        <v>6</v>
+        <v>122</v>
+      </c>
+      <c r="G15" t="s">
+        <v>129</v>
       </c>
       <c r="H15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D16" t="s">
         <v>5</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="78">
         <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>53</v>
+        <v>123</v>
+      </c>
+      <c r="G16" s="79" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1346,24 +1428,24 @@
       <c r="A18" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="16"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="15"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="10"/>
       <c r="D19" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="13">
         <v>0</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>16</v>
@@ -1374,21 +1456,21 @@
         <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="11">
         <f>(22.5/64*52+20.2/58*52)/2</f>
         <v>18.195797413793102</v>
       </c>
       <c r="F20" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G20" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H20" t="s">
         <v>43</v>
@@ -1399,17 +1481,17 @@
         <v>41</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="14">
         <f>E20</f>
         <v>18.195797413793102</v>
       </c>
-      <c r="F21" s="15" t="str">
+      <c r="F21" s="14" t="str">
         <f>F20</f>
         <v>kg/head/year</v>
       </c>
@@ -1419,17 +1501,17 @@
         <v>41</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="14">
         <f>E20</f>
         <v>18.195797413793102</v>
       </c>
-      <c r="F22" s="15" t="str">
+      <c r="F22" s="14" t="str">
         <f>F21</f>
         <v>kg/head/year</v>
       </c>
@@ -1439,18 +1521,18 @@
         <v>42</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="12">
+      <c r="E23" s="11">
         <f>20/60*52</f>
         <v>17.333333333333332</v>
       </c>
       <c r="F23" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H23" t="s">
         <v>44</v>
@@ -1461,17 +1543,17 @@
         <v>42</v>
       </c>
       <c r="B24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" t="s">
         <v>40</v>
       </c>
-      <c r="E24" s="15">
+      <c r="E24" s="14">
         <f>E23</f>
         <v>17.333333333333332</v>
       </c>
-      <c r="F24" s="15" t="str">
+      <c r="F24" s="14" t="str">
         <f>F23</f>
         <v>kg/head/year</v>
       </c>
@@ -1481,29 +1563,29 @@
         <v>42</v>
       </c>
       <c r="B25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" t="s">
         <v>40</v>
       </c>
-      <c r="E25" s="15">
+      <c r="E25" s="14">
         <f>E23</f>
         <v>17.333333333333332</v>
       </c>
-      <c r="F25" s="15" t="str">
+      <c r="F25" s="14" t="str">
         <f>F24</f>
         <v>kg/head/year</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C26" s="8"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -1524,7 +1606,7 @@
         <v>15</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1537,18 +1619,18 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
-      <c r="F32" s="71" t="s">
-        <v>112</v>
+      <c r="F32" s="70" t="s">
+        <v>107</v>
       </c>
       <c r="G32" s="6"/>
-      <c r="H32" s="71" t="s">
-        <v>115</v>
+      <c r="H32" s="70" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1556,10 +1638,10 @@
         <v>41</v>
       </c>
       <c r="B33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D33" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E33" s="4">
         <f>INDEX('Feed rations'!$W$19:$AA$19,MATCH(B33,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -1571,10 +1653,10 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D34" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E34" s="4">
         <f>INDEX('Feed rations'!$W$19:$AA$19,MATCH(B34,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -1586,10 +1668,10 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D35" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E35" s="4">
         <f>INDEX('Feed rations'!$W$19:$AA$19,MATCH(B35,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -1601,10 +1683,10 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D36" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E36" s="4">
         <f>INDEX('Feed rations'!$W$19:$AA$19,MATCH(B36,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -1616,10 +1698,10 @@
         <v>41</v>
       </c>
       <c r="B37" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D37" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E37" s="4">
         <f>INDEX('Feed rations'!$W$19:$AA$19,MATCH(B37,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -1631,10 +1713,10 @@
         <v>42</v>
       </c>
       <c r="B39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D39" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E39" s="4">
         <f>INDEX('Feed rations'!$AB$19:$AF$19,MATCH(B39,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -1646,10 +1728,10 @@
         <v>42</v>
       </c>
       <c r="B40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D40" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E40" s="4">
         <f>INDEX('Feed rations'!$AB$19:$AF$19,MATCH(B40,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -1661,10 +1743,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D41" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E41" s="4">
         <f>INDEX('Feed rations'!$AB$19:$AF$19,MATCH(B41,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -1676,10 +1758,10 @@
         <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D42" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E42" s="4">
         <f>INDEX('Feed rations'!$AB$19:$AF$19,MATCH(B42,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -1691,10 +1773,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D43" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E43" s="4">
         <f>INDEX('Feed rations'!$AB$19:$AF$19,MATCH(B43,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -1703,18 +1785,18 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
-      <c r="F45" s="71" t="s">
-        <v>114</v>
+      <c r="F45" s="70" t="s">
+        <v>109</v>
       </c>
       <c r="G45" s="6"/>
-      <c r="H45" s="71" t="s">
-        <v>115</v>
+      <c r="H45" s="70" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -1722,13 +1804,13 @@
         <v>41</v>
       </c>
       <c r="B46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C46" t="s">
         <v>17</v>
       </c>
       <c r="D46" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E46" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C46,'Feed rations'!$V$5:$V$17,0),MATCH(B46,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -1740,13 +1822,13 @@
         <v>41</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C47" t="s">
         <v>19</v>
       </c>
       <c r="D47" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E47" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C47,'Feed rations'!$V$5:$V$17,0),MATCH(B47,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -1758,13 +1840,13 @@
         <v>41</v>
       </c>
       <c r="B48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C48" t="s">
         <v>18</v>
       </c>
       <c r="D48" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E48" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C48,'Feed rations'!$V$5:$V$17,0),MATCH(B48,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -1776,13 +1858,13 @@
         <v>41</v>
       </c>
       <c r="B49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C49" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D49" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E49" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C49,'Feed rations'!$V$5:$V$17,0),MATCH(B49,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -1794,13 +1876,13 @@
         <v>41</v>
       </c>
       <c r="B50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C50" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D50" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E50" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C50,'Feed rations'!$V$5:$V$17,0),MATCH(B50,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -1812,13 +1894,13 @@
         <v>41</v>
       </c>
       <c r="B51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C51" t="s">
         <v>20</v>
       </c>
       <c r="D51" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E51" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C51,'Feed rations'!$V$5:$V$17,0),MATCH(B51,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -1830,13 +1912,13 @@
         <v>41</v>
       </c>
       <c r="B52" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C52" t="s">
         <v>21</v>
       </c>
       <c r="D52" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E52" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C52,'Feed rations'!$V$5:$V$17,0),MATCH(B52,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -1848,13 +1930,13 @@
         <v>41</v>
       </c>
       <c r="B53" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C53" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D53" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E53" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C53,'Feed rations'!$V$5:$V$17,0),MATCH(B53,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -1866,13 +1948,13 @@
         <v>41</v>
       </c>
       <c r="B54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C54" t="s">
         <v>22</v>
       </c>
       <c r="D54" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E54" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C54,'Feed rations'!$V$5:$V$17,0),MATCH(B54,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -1884,13 +1966,13 @@
         <v>41</v>
       </c>
       <c r="B55" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C55" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D55" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E55" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C55,'Feed rations'!$V$5:$V$17,0),MATCH(B55,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -1902,13 +1984,13 @@
         <v>41</v>
       </c>
       <c r="B56" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C56" t="s">
         <v>23</v>
       </c>
       <c r="D56" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E56" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C56,'Feed rations'!$V$5:$V$17,0),MATCH(B56,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -1920,13 +2002,13 @@
         <v>41</v>
       </c>
       <c r="B57" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C57" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D57" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E57" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C57,'Feed rations'!$V$5:$V$17,0),MATCH(B57,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -1938,13 +2020,13 @@
         <v>41</v>
       </c>
       <c r="B58" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C58" t="s">
         <v>27</v>
       </c>
       <c r="D58" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E58" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C58,'Feed rations'!$V$5:$V$17,0),MATCH(B58,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -1956,13 +2038,13 @@
         <v>41</v>
       </c>
       <c r="B59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C59" t="s">
         <v>17</v>
       </c>
       <c r="D59" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E59" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C59,'Feed rations'!$V$5:$V$17,0),MATCH(B59,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -1974,13 +2056,13 @@
         <v>41</v>
       </c>
       <c r="B60" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C60" t="s">
         <v>19</v>
       </c>
       <c r="D60" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E60" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C60,'Feed rations'!$V$5:$V$17,0),MATCH(B60,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -1992,13 +2074,13 @@
         <v>41</v>
       </c>
       <c r="B61" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C61" t="s">
         <v>18</v>
       </c>
       <c r="D61" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E61" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C61,'Feed rations'!$V$5:$V$17,0),MATCH(B61,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2010,13 +2092,13 @@
         <v>41</v>
       </c>
       <c r="B62" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C62" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D62" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E62" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C62,'Feed rations'!$V$5:$V$17,0),MATCH(B62,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2028,13 +2110,13 @@
         <v>41</v>
       </c>
       <c r="B63" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C63" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D63" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E63" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C63,'Feed rations'!$V$5:$V$17,0),MATCH(B63,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2046,13 +2128,13 @@
         <v>41</v>
       </c>
       <c r="B64" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C64" t="s">
         <v>20</v>
       </c>
       <c r="D64" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E64" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C64,'Feed rations'!$V$5:$V$17,0),MATCH(B64,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2064,13 +2146,13 @@
         <v>41</v>
       </c>
       <c r="B65" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C65" t="s">
         <v>21</v>
       </c>
       <c r="D65" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E65" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C65,'Feed rations'!$V$5:$V$17,0),MATCH(B65,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2082,13 +2164,13 @@
         <v>41</v>
       </c>
       <c r="B66" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C66" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D66" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E66" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C66,'Feed rations'!$V$5:$V$17,0),MATCH(B66,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2100,13 +2182,13 @@
         <v>41</v>
       </c>
       <c r="B67" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C67" t="s">
         <v>22</v>
       </c>
       <c r="D67" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E67" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C67,'Feed rations'!$V$5:$V$17,0),MATCH(B67,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2118,13 +2200,13 @@
         <v>41</v>
       </c>
       <c r="B68" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C68" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D68" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E68" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C68,'Feed rations'!$V$5:$V$17,0),MATCH(B68,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2136,13 +2218,13 @@
         <v>41</v>
       </c>
       <c r="B69" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C69" t="s">
         <v>23</v>
       </c>
       <c r="D69" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E69" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C69,'Feed rations'!$V$5:$V$17,0),MATCH(B69,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2154,13 +2236,13 @@
         <v>41</v>
       </c>
       <c r="B70" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C70" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D70" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E70" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C70,'Feed rations'!$V$5:$V$17,0),MATCH(B70,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2172,13 +2254,13 @@
         <v>41</v>
       </c>
       <c r="B71" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C71" t="s">
         <v>27</v>
       </c>
       <c r="D71" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E71" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C71,'Feed rations'!$V$5:$V$17,0),MATCH(B71,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2190,13 +2272,13 @@
         <v>41</v>
       </c>
       <c r="B72" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C72" t="s">
         <v>17</v>
       </c>
       <c r="D72" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E72" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C72,'Feed rations'!$V$5:$V$17,0),MATCH(B72,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2208,13 +2290,13 @@
         <v>41</v>
       </c>
       <c r="B73" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C73" t="s">
         <v>19</v>
       </c>
       <c r="D73" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E73" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C73,'Feed rations'!$V$5:$V$17,0),MATCH(B73,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2226,13 +2308,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C74" t="s">
         <v>18</v>
       </c>
       <c r="D74" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E74" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C74,'Feed rations'!$V$5:$V$17,0),MATCH(B74,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2244,13 +2326,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C75" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D75" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E75" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C75,'Feed rations'!$V$5:$V$17,0),MATCH(B75,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2262,13 +2344,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C76" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D76" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E76" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C76,'Feed rations'!$V$5:$V$17,0),MATCH(B76,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2280,13 +2362,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C77" t="s">
         <v>20</v>
       </c>
       <c r="D77" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E77" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C77,'Feed rations'!$V$5:$V$17,0),MATCH(B77,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2298,13 +2380,13 @@
         <v>41</v>
       </c>
       <c r="B78" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C78" t="s">
         <v>21</v>
       </c>
       <c r="D78" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E78" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C78,'Feed rations'!$V$5:$V$17,0),MATCH(B78,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2316,13 +2398,13 @@
         <v>41</v>
       </c>
       <c r="B79" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C79" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D79" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E79" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C79,'Feed rations'!$V$5:$V$17,0),MATCH(B79,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2334,13 +2416,13 @@
         <v>41</v>
       </c>
       <c r="B80" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C80" t="s">
         <v>22</v>
       </c>
       <c r="D80" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E80" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C80,'Feed rations'!$V$5:$V$17,0),MATCH(B80,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2352,13 +2434,13 @@
         <v>41</v>
       </c>
       <c r="B81" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C81" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D81" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E81" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C81,'Feed rations'!$V$5:$V$17,0),MATCH(B81,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2370,13 +2452,13 @@
         <v>41</v>
       </c>
       <c r="B82" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C82" t="s">
         <v>23</v>
       </c>
       <c r="D82" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E82" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C82,'Feed rations'!$V$5:$V$17,0),MATCH(B82,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2388,13 +2470,13 @@
         <v>41</v>
       </c>
       <c r="B83" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C83" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D83" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E83" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C83,'Feed rations'!$V$5:$V$17,0),MATCH(B83,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2406,13 +2488,13 @@
         <v>41</v>
       </c>
       <c r="B84" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C84" t="s">
         <v>27</v>
       </c>
       <c r="D84" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E84" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C84,'Feed rations'!$V$5:$V$17,0),MATCH(B84,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2424,13 +2506,13 @@
         <v>41</v>
       </c>
       <c r="B85" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C85" t="s">
         <v>17</v>
       </c>
       <c r="D85" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E85" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C85,'Feed rations'!$V$5:$V$17,0),MATCH(B85,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2442,13 +2524,13 @@
         <v>41</v>
       </c>
       <c r="B86" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C86" t="s">
         <v>19</v>
       </c>
       <c r="D86" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E86" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C86,'Feed rations'!$V$5:$V$17,0),MATCH(B86,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2460,13 +2542,13 @@
         <v>41</v>
       </c>
       <c r="B87" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C87" t="s">
         <v>18</v>
       </c>
       <c r="D87" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E87" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C87,'Feed rations'!$V$5:$V$17,0),MATCH(B87,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2478,13 +2560,13 @@
         <v>41</v>
       </c>
       <c r="B88" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C88" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D88" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E88" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C88,'Feed rations'!$V$5:$V$17,0),MATCH(B88,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2496,13 +2578,13 @@
         <v>41</v>
       </c>
       <c r="B89" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C89" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D89" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E89" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C89,'Feed rations'!$V$5:$V$17,0),MATCH(B89,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2514,13 +2596,13 @@
         <v>41</v>
       </c>
       <c r="B90" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C90" t="s">
         <v>20</v>
       </c>
       <c r="D90" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E90" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C90,'Feed rations'!$V$5:$V$17,0),MATCH(B90,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2532,13 +2614,13 @@
         <v>41</v>
       </c>
       <c r="B91" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C91" t="s">
         <v>21</v>
       </c>
       <c r="D91" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E91" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C91,'Feed rations'!$V$5:$V$17,0),MATCH(B91,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2550,13 +2632,13 @@
         <v>41</v>
       </c>
       <c r="B92" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C92" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D92" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E92" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C92,'Feed rations'!$V$5:$V$17,0),MATCH(B92,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2568,13 +2650,13 @@
         <v>41</v>
       </c>
       <c r="B93" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C93" t="s">
         <v>22</v>
       </c>
       <c r="D93" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E93" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C93,'Feed rations'!$V$5:$V$17,0),MATCH(B93,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2586,13 +2668,13 @@
         <v>41</v>
       </c>
       <c r="B94" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C94" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D94" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E94" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C94,'Feed rations'!$V$5:$V$17,0),MATCH(B94,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2604,13 +2686,13 @@
         <v>41</v>
       </c>
       <c r="B95" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C95" t="s">
         <v>23</v>
       </c>
       <c r="D95" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E95" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C95,'Feed rations'!$V$5:$V$17,0),MATCH(B95,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2622,13 +2704,13 @@
         <v>41</v>
       </c>
       <c r="B96" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C96" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D96" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E96" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C96,'Feed rations'!$V$5:$V$17,0),MATCH(B96,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2640,13 +2722,13 @@
         <v>41</v>
       </c>
       <c r="B97" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C97" t="s">
         <v>27</v>
       </c>
       <c r="D97" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E97" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C97,'Feed rations'!$V$5:$V$17,0),MATCH(B97,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2658,13 +2740,13 @@
         <v>41</v>
       </c>
       <c r="B98" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C98" t="s">
         <v>17</v>
       </c>
       <c r="D98" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E98" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C98,'Feed rations'!$V$5:$V$17,0),MATCH(B98,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2676,13 +2758,13 @@
         <v>41</v>
       </c>
       <c r="B99" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C99" t="s">
         <v>19</v>
       </c>
       <c r="D99" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E99" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C99,'Feed rations'!$V$5:$V$17,0),MATCH(B99,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2694,13 +2776,13 @@
         <v>41</v>
       </c>
       <c r="B100" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C100" t="s">
         <v>18</v>
       </c>
       <c r="D100" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E100" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C100,'Feed rations'!$V$5:$V$17,0),MATCH(B100,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2712,13 +2794,13 @@
         <v>41</v>
       </c>
       <c r="B101" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C101" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D101" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E101" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C101,'Feed rations'!$V$5:$V$17,0),MATCH(B101,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2730,13 +2812,13 @@
         <v>41</v>
       </c>
       <c r="B102" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C102" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D102" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E102" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C102,'Feed rations'!$V$5:$V$17,0),MATCH(B102,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2748,13 +2830,13 @@
         <v>41</v>
       </c>
       <c r="B103" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C103" t="s">
         <v>20</v>
       </c>
       <c r="D103" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E103" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C103,'Feed rations'!$V$5:$V$17,0),MATCH(B103,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2766,13 +2848,13 @@
         <v>41</v>
       </c>
       <c r="B104" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C104" t="s">
         <v>21</v>
       </c>
       <c r="D104" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E104" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C104,'Feed rations'!$V$5:$V$17,0),MATCH(B104,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2784,13 +2866,13 @@
         <v>41</v>
       </c>
       <c r="B105" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C105" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D105" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E105" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C105,'Feed rations'!$V$5:$V$17,0),MATCH(B105,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2802,13 +2884,13 @@
         <v>41</v>
       </c>
       <c r="B106" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C106" t="s">
         <v>22</v>
       </c>
       <c r="D106" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E106" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C106,'Feed rations'!$V$5:$V$17,0),MATCH(B106,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2820,13 +2902,13 @@
         <v>41</v>
       </c>
       <c r="B107" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C107" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D107" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E107" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C107,'Feed rations'!$V$5:$V$17,0),MATCH(B107,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2838,13 +2920,13 @@
         <v>41</v>
       </c>
       <c r="B108" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C108" t="s">
         <v>23</v>
       </c>
       <c r="D108" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E108" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C108,'Feed rations'!$V$5:$V$17,0),MATCH(B108,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2856,13 +2938,13 @@
         <v>41</v>
       </c>
       <c r="B109" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C109" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D109" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E109" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C109,'Feed rations'!$V$5:$V$17,0),MATCH(B109,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2874,13 +2956,13 @@
         <v>41</v>
       </c>
       <c r="B110" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C110" t="s">
         <v>27</v>
       </c>
       <c r="D110" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E110" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C110,'Feed rations'!$V$5:$V$17,0),MATCH(B110,'Feed rations'!$W$4:$AA$4,0))</f>
@@ -2895,13 +2977,13 @@
         <v>42</v>
       </c>
       <c r="B112" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C112" t="s">
         <v>17</v>
       </c>
       <c r="D112" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E112" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C112,'Feed rations'!$V$5:$V$17,0),MATCH(B112,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -2913,13 +2995,13 @@
         <v>42</v>
       </c>
       <c r="B113" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C113" t="s">
         <v>19</v>
       </c>
       <c r="D113" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E113" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C113,'Feed rations'!$V$5:$V$17,0),MATCH(B113,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -2931,13 +3013,13 @@
         <v>42</v>
       </c>
       <c r="B114" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C114" t="s">
         <v>18</v>
       </c>
       <c r="D114" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E114" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C114,'Feed rations'!$V$5:$V$17,0),MATCH(B114,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -2949,13 +3031,13 @@
         <v>42</v>
       </c>
       <c r="B115" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C115" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D115" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E115" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C115,'Feed rations'!$V$5:$V$17,0),MATCH(B115,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -2967,13 +3049,13 @@
         <v>42</v>
       </c>
       <c r="B116" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C116" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D116" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E116" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C116,'Feed rations'!$V$5:$V$17,0),MATCH(B116,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -2985,13 +3067,13 @@
         <v>42</v>
       </c>
       <c r="B117" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C117" t="s">
         <v>20</v>
       </c>
       <c r="D117" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E117" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C117,'Feed rations'!$V$5:$V$17,0),MATCH(B117,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3003,13 +3085,13 @@
         <v>42</v>
       </c>
       <c r="B118" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C118" t="s">
         <v>21</v>
       </c>
       <c r="D118" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E118" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C118,'Feed rations'!$V$5:$V$17,0),MATCH(B118,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3021,13 +3103,13 @@
         <v>42</v>
       </c>
       <c r="B119" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C119" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D119" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E119" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C119,'Feed rations'!$V$5:$V$17,0),MATCH(B119,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3039,13 +3121,13 @@
         <v>42</v>
       </c>
       <c r="B120" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C120" t="s">
         <v>22</v>
       </c>
       <c r="D120" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E120" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C120,'Feed rations'!$V$5:$V$17,0),MATCH(B120,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3057,13 +3139,13 @@
         <v>42</v>
       </c>
       <c r="B121" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C121" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D121" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E121" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C121,'Feed rations'!$V$5:$V$17,0),MATCH(B121,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3075,13 +3157,13 @@
         <v>42</v>
       </c>
       <c r="B122" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C122" t="s">
         <v>23</v>
       </c>
       <c r="D122" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E122" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C122,'Feed rations'!$V$5:$V$17,0),MATCH(B122,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3093,13 +3175,13 @@
         <v>42</v>
       </c>
       <c r="B123" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C123" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D123" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E123" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C123,'Feed rations'!$V$5:$V$17,0),MATCH(B123,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3111,13 +3193,13 @@
         <v>42</v>
       </c>
       <c r="B124" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C124" t="s">
         <v>27</v>
       </c>
       <c r="D124" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E124" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C124,'Feed rations'!$V$5:$V$17,0),MATCH(B124,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3129,13 +3211,13 @@
         <v>42</v>
       </c>
       <c r="B125" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C125" t="s">
         <v>17</v>
       </c>
       <c r="D125" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E125" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C125,'Feed rations'!$V$5:$V$17,0),MATCH(B125,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3147,13 +3229,13 @@
         <v>42</v>
       </c>
       <c r="B126" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C126" t="s">
         <v>19</v>
       </c>
       <c r="D126" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E126" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C126,'Feed rations'!$V$5:$V$17,0),MATCH(B126,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3165,13 +3247,13 @@
         <v>42</v>
       </c>
       <c r="B127" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C127" t="s">
         <v>18</v>
       </c>
       <c r="D127" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E127" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C127,'Feed rations'!$V$5:$V$17,0),MATCH(B127,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3183,13 +3265,13 @@
         <v>42</v>
       </c>
       <c r="B128" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C128" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D128" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E128" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C128,'Feed rations'!$V$5:$V$17,0),MATCH(B128,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3201,13 +3283,13 @@
         <v>42</v>
       </c>
       <c r="B129" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C129" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D129" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E129" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C129,'Feed rations'!$V$5:$V$17,0),MATCH(B129,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3219,13 +3301,13 @@
         <v>42</v>
       </c>
       <c r="B130" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C130" t="s">
         <v>20</v>
       </c>
       <c r="D130" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E130" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C130,'Feed rations'!$V$5:$V$17,0),MATCH(B130,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3237,13 +3319,13 @@
         <v>42</v>
       </c>
       <c r="B131" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C131" t="s">
         <v>21</v>
       </c>
       <c r="D131" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E131" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C131,'Feed rations'!$V$5:$V$17,0),MATCH(B131,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3255,13 +3337,13 @@
         <v>42</v>
       </c>
       <c r="B132" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C132" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D132" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E132" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C132,'Feed rations'!$V$5:$V$17,0),MATCH(B132,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3273,13 +3355,13 @@
         <v>42</v>
       </c>
       <c r="B133" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C133" t="s">
         <v>22</v>
       </c>
       <c r="D133" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E133" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C133,'Feed rations'!$V$5:$V$17,0),MATCH(B133,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3291,13 +3373,13 @@
         <v>42</v>
       </c>
       <c r="B134" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C134" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D134" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E134" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C134,'Feed rations'!$V$5:$V$17,0),MATCH(B134,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3309,13 +3391,13 @@
         <v>42</v>
       </c>
       <c r="B135" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C135" t="s">
         <v>23</v>
       </c>
       <c r="D135" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E135" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C135,'Feed rations'!$V$5:$V$17,0),MATCH(B135,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3327,13 +3409,13 @@
         <v>42</v>
       </c>
       <c r="B136" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C136" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D136" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E136" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C136,'Feed rations'!$V$5:$V$17,0),MATCH(B136,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3345,13 +3427,13 @@
         <v>42</v>
       </c>
       <c r="B137" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C137" t="s">
         <v>27</v>
       </c>
       <c r="D137" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E137" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C137,'Feed rations'!$V$5:$V$17,0),MATCH(B137,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3363,13 +3445,13 @@
         <v>42</v>
       </c>
       <c r="B138" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C138" t="s">
         <v>17</v>
       </c>
       <c r="D138" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E138" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C138,'Feed rations'!$V$5:$V$17,0),MATCH(B138,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3381,13 +3463,13 @@
         <v>42</v>
       </c>
       <c r="B139" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C139" t="s">
         <v>19</v>
       </c>
       <c r="D139" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E139" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C139,'Feed rations'!$V$5:$V$17,0),MATCH(B139,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3399,13 +3481,13 @@
         <v>42</v>
       </c>
       <c r="B140" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C140" t="s">
         <v>18</v>
       </c>
       <c r="D140" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E140" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C140,'Feed rations'!$V$5:$V$17,0),MATCH(B140,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3417,13 +3499,13 @@
         <v>42</v>
       </c>
       <c r="B141" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C141" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D141" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E141" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C141,'Feed rations'!$V$5:$V$17,0),MATCH(B141,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3435,13 +3517,13 @@
         <v>42</v>
       </c>
       <c r="B142" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C142" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D142" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E142" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C142,'Feed rations'!$V$5:$V$17,0),MATCH(B142,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3453,13 +3535,13 @@
         <v>42</v>
       </c>
       <c r="B143" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C143" t="s">
         <v>20</v>
       </c>
       <c r="D143" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E143" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C143,'Feed rations'!$V$5:$V$17,0),MATCH(B143,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3471,13 +3553,13 @@
         <v>42</v>
       </c>
       <c r="B144" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C144" t="s">
         <v>21</v>
       </c>
       <c r="D144" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E144" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C144,'Feed rations'!$V$5:$V$17,0),MATCH(B144,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3489,13 +3571,13 @@
         <v>42</v>
       </c>
       <c r="B145" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C145" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D145" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E145" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C145,'Feed rations'!$V$5:$V$17,0),MATCH(B145,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3507,13 +3589,13 @@
         <v>42</v>
       </c>
       <c r="B146" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C146" t="s">
         <v>22</v>
       </c>
       <c r="D146" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E146" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C146,'Feed rations'!$V$5:$V$17,0),MATCH(B146,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3525,13 +3607,13 @@
         <v>42</v>
       </c>
       <c r="B147" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C147" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D147" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E147" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C147,'Feed rations'!$V$5:$V$17,0),MATCH(B147,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3543,13 +3625,13 @@
         <v>42</v>
       </c>
       <c r="B148" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C148" t="s">
         <v>23</v>
       </c>
       <c r="D148" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E148" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C148,'Feed rations'!$V$5:$V$17,0),MATCH(B148,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3561,13 +3643,13 @@
         <v>42</v>
       </c>
       <c r="B149" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C149" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D149" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E149" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C149,'Feed rations'!$V$5:$V$17,0),MATCH(B149,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3579,13 +3661,13 @@
         <v>42</v>
       </c>
       <c r="B150" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C150" t="s">
         <v>27</v>
       </c>
       <c r="D150" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E150" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C150,'Feed rations'!$V$5:$V$17,0),MATCH(B150,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3597,13 +3679,13 @@
         <v>42</v>
       </c>
       <c r="B151" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C151" t="s">
         <v>17</v>
       </c>
       <c r="D151" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E151" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C151,'Feed rations'!$V$5:$V$17,0),MATCH(B151,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3615,13 +3697,13 @@
         <v>42</v>
       </c>
       <c r="B152" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C152" t="s">
         <v>19</v>
       </c>
       <c r="D152" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E152" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C152,'Feed rations'!$V$5:$V$17,0),MATCH(B152,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3633,13 +3715,13 @@
         <v>42</v>
       </c>
       <c r="B153" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C153" t="s">
         <v>18</v>
       </c>
       <c r="D153" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E153" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C153,'Feed rations'!$V$5:$V$17,0),MATCH(B153,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3651,13 +3733,13 @@
         <v>42</v>
       </c>
       <c r="B154" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C154" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D154" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E154" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C154,'Feed rations'!$V$5:$V$17,0),MATCH(B154,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3669,13 +3751,13 @@
         <v>42</v>
       </c>
       <c r="B155" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C155" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D155" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E155" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C155,'Feed rations'!$V$5:$V$17,0),MATCH(B155,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3687,13 +3769,13 @@
         <v>42</v>
       </c>
       <c r="B156" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C156" t="s">
         <v>20</v>
       </c>
       <c r="D156" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E156" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C156,'Feed rations'!$V$5:$V$17,0),MATCH(B156,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3705,13 +3787,13 @@
         <v>42</v>
       </c>
       <c r="B157" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C157" t="s">
         <v>21</v>
       </c>
       <c r="D157" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E157" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C157,'Feed rations'!$V$5:$V$17,0),MATCH(B157,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3723,13 +3805,13 @@
         <v>42</v>
       </c>
       <c r="B158" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C158" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D158" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E158" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C158,'Feed rations'!$V$5:$V$17,0),MATCH(B158,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3741,13 +3823,13 @@
         <v>42</v>
       </c>
       <c r="B159" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C159" t="s">
         <v>22</v>
       </c>
       <c r="D159" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E159" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C159,'Feed rations'!$V$5:$V$17,0),MATCH(B159,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3759,13 +3841,13 @@
         <v>42</v>
       </c>
       <c r="B160" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C160" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D160" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E160" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C160,'Feed rations'!$V$5:$V$17,0),MATCH(B160,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3777,13 +3859,13 @@
         <v>42</v>
       </c>
       <c r="B161" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C161" t="s">
         <v>23</v>
       </c>
       <c r="D161" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E161" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C161,'Feed rations'!$V$5:$V$17,0),MATCH(B161,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3795,13 +3877,13 @@
         <v>42</v>
       </c>
       <c r="B162" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C162" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D162" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E162" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C162,'Feed rations'!$V$5:$V$17,0),MATCH(B162,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3813,13 +3895,13 @@
         <v>42</v>
       </c>
       <c r="B163" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C163" t="s">
         <v>27</v>
       </c>
       <c r="D163" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E163" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C163,'Feed rations'!$V$5:$V$17,0),MATCH(B163,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3831,13 +3913,13 @@
         <v>42</v>
       </c>
       <c r="B164" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C164" t="s">
         <v>17</v>
       </c>
       <c r="D164" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E164" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C164,'Feed rations'!$V$5:$V$17,0),MATCH(B164,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3849,13 +3931,13 @@
         <v>42</v>
       </c>
       <c r="B165" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C165" t="s">
         <v>19</v>
       </c>
       <c r="D165" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E165" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C165,'Feed rations'!$V$5:$V$17,0),MATCH(B165,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3867,13 +3949,13 @@
         <v>42</v>
       </c>
       <c r="B166" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C166" t="s">
         <v>18</v>
       </c>
       <c r="D166" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E166" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C166,'Feed rations'!$V$5:$V$17,0),MATCH(B166,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3885,13 +3967,13 @@
         <v>42</v>
       </c>
       <c r="B167" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C167" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D167" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E167" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C167,'Feed rations'!$V$5:$V$17,0),MATCH(B167,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3903,13 +3985,13 @@
         <v>42</v>
       </c>
       <c r="B168" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C168" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D168" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E168" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C168,'Feed rations'!$V$5:$V$17,0),MATCH(B168,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3921,13 +4003,13 @@
         <v>42</v>
       </c>
       <c r="B169" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C169" t="s">
         <v>20</v>
       </c>
       <c r="D169" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E169" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C169,'Feed rations'!$V$5:$V$17,0),MATCH(B169,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3939,13 +4021,13 @@
         <v>42</v>
       </c>
       <c r="B170" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C170" t="s">
         <v>21</v>
       </c>
       <c r="D170" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E170" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C170,'Feed rations'!$V$5:$V$17,0),MATCH(B170,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3957,13 +4039,13 @@
         <v>42</v>
       </c>
       <c r="B171" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C171" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D171" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E171" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C171,'Feed rations'!$V$5:$V$17,0),MATCH(B171,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3975,13 +4057,13 @@
         <v>42</v>
       </c>
       <c r="B172" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C172" t="s">
         <v>22</v>
       </c>
       <c r="D172" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E172" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C172,'Feed rations'!$V$5:$V$17,0),MATCH(B172,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -3993,13 +4075,13 @@
         <v>42</v>
       </c>
       <c r="B173" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C173" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D173" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E173" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C173,'Feed rations'!$V$5:$V$17,0),MATCH(B173,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -4011,13 +4093,13 @@
         <v>42</v>
       </c>
       <c r="B174" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C174" t="s">
         <v>23</v>
       </c>
       <c r="D174" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E174" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C174,'Feed rations'!$V$5:$V$17,0),MATCH(B174,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -4029,13 +4111,13 @@
         <v>42</v>
       </c>
       <c r="B175" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C175" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D175" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E175" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C175,'Feed rations'!$V$5:$V$17,0),MATCH(B175,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -4047,13 +4129,13 @@
         <v>42</v>
       </c>
       <c r="B176" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C176" t="s">
         <v>27</v>
       </c>
       <c r="D176" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E176" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C176,'Feed rations'!$V$5:$V$17,0),MATCH(B176,'Feed rations'!$AB$4:$AF$4,0))</f>
@@ -4079,7 +4161,7 @@
   <sheetData>
     <row r="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="F1" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
@@ -4098,199 +4180,199 @@
       <c r="T1" s="2"/>
     </row>
     <row r="2" spans="2:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D2" s="22"/>
-      <c r="E2" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="F2" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="63" t="s">
-        <v>77</v>
-      </c>
-      <c r="L2" s="56"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="53" t="str">
+      <c r="D2" s="21"/>
+      <c r="E2" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F2" s="52" t="s">
+        <v>117</v>
+      </c>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="62" t="s">
+        <v>118</v>
+      </c>
+      <c r="L2" s="55"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="52" t="str">
         <f>F2</f>
-        <v>Sonesson 2008</v>
-      </c>
-      <c r="O2" s="54"/>
-      <c r="P2" s="54"/>
-      <c r="Q2" s="54"/>
-      <c r="R2" s="54"/>
-      <c r="S2" s="63" t="str">
+        <v>Sonesson et al (2008)</v>
+      </c>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
+      <c r="Q2" s="53"/>
+      <c r="R2" s="53"/>
+      <c r="S2" s="62" t="str">
         <f>K2</f>
-        <v>Carlsson</v>
-      </c>
-      <c r="T2" s="56"/>
-      <c r="U2" s="22"/>
-      <c r="W2" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="X2" s="49"/>
-      <c r="Y2" s="49"/>
-      <c r="Z2" s="49"/>
-      <c r="AA2" s="49"/>
-      <c r="AB2" s="49"/>
-      <c r="AC2" s="49"/>
-      <c r="AD2" s="49"/>
-      <c r="AE2" s="49"/>
-      <c r="AF2" s="49"/>
+        <v>Carlsson et al (2009)</v>
+      </c>
+      <c r="T2" s="55"/>
+      <c r="U2" s="21"/>
+      <c r="W2" s="47" t="s">
+        <v>86</v>
+      </c>
+      <c r="X2" s="48"/>
+      <c r="Y2" s="48"/>
+      <c r="Z2" s="48"/>
+      <c r="AA2" s="48"/>
+      <c r="AB2" s="48"/>
+      <c r="AC2" s="48"/>
+      <c r="AD2" s="48"/>
+      <c r="AE2" s="48"/>
+      <c r="AF2" s="48"/>
     </row>
     <row r="3" spans="2:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D3" s="22"/>
-      <c r="E3" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="F3" s="53" t="s">
+      <c r="D3" s="21"/>
+      <c r="E3" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54" t="s">
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="54"/>
-      <c r="K3" s="63" t="s">
-        <v>78</v>
-      </c>
-      <c r="L3" s="56"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="53" t="str">
+      <c r="J3" s="53"/>
+      <c r="K3" s="62" t="s">
+        <v>73</v>
+      </c>
+      <c r="L3" s="55"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="52" t="str">
         <f t="shared" ref="N3:N4" si="0">F3</f>
         <v>A</v>
       </c>
-      <c r="O3" s="54"/>
-      <c r="P3" s="54"/>
-      <c r="Q3" s="54" t="str">
+      <c r="O3" s="53"/>
+      <c r="P3" s="53"/>
+      <c r="Q3" s="53" t="str">
         <f t="shared" ref="Q3:Q4" si="1">I3</f>
         <v>B</v>
       </c>
-      <c r="R3" s="54"/>
-      <c r="S3" s="63" t="str">
+      <c r="R3" s="53"/>
+      <c r="S3" s="62" t="str">
         <f t="shared" ref="S3:S4" si="2">K3</f>
         <v>N/A</v>
       </c>
-      <c r="T3" s="56"/>
-      <c r="U3" s="22"/>
-      <c r="V3" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="W3" s="53" t="s">
-        <v>41</v>
-      </c>
-      <c r="X3" s="54"/>
-      <c r="Y3" s="54"/>
-      <c r="Z3" s="54"/>
-      <c r="AA3" s="68"/>
-      <c r="AB3" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="AC3" s="55"/>
-      <c r="AD3" s="55"/>
-      <c r="AE3" s="55"/>
-      <c r="AF3" s="56"/>
-      <c r="AG3" s="21"/>
+      <c r="T3" s="55"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="W3" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="X3" s="53"/>
+      <c r="Y3" s="53"/>
+      <c r="Z3" s="53"/>
+      <c r="AA3" s="67"/>
+      <c r="AB3" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC3" s="54"/>
+      <c r="AD3" s="54"/>
+      <c r="AE3" s="54"/>
+      <c r="AF3" s="55"/>
+      <c r="AG3" s="20"/>
     </row>
     <row r="4" spans="2:33" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="G4" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="F4" s="50" t="s">
+      <c r="H4" s="50" t="s">
+        <v>70</v>
+      </c>
+      <c r="I4" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="J4" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="G4" s="51" t="s">
-        <v>73</v>
-      </c>
-      <c r="H4" s="51" t="s">
+      <c r="K4" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="I4" s="51" t="s">
+      <c r="L4" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="J4" s="51" t="s">
-        <v>76</v>
-      </c>
-      <c r="K4" s="64" t="s">
-        <v>79</v>
-      </c>
-      <c r="L4" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="M4" s="21"/>
-      <c r="N4" s="50" t="str">
+      <c r="M4" s="20"/>
+      <c r="N4" s="49" t="str">
         <f t="shared" si="0"/>
         <v>Värp fri start</v>
       </c>
-      <c r="O4" s="51" t="str">
+      <c r="O4" s="50" t="str">
         <f>G4</f>
         <v>Värp fri max</v>
       </c>
-      <c r="P4" s="51" t="str">
+      <c r="P4" s="50" t="str">
         <f>H4</f>
         <v>Värp fri slut</v>
       </c>
-      <c r="Q4" s="51" t="str">
+      <c r="Q4" s="50" t="str">
         <f t="shared" si="1"/>
         <v>Värp 95</v>
       </c>
-      <c r="R4" s="51" t="str">
+      <c r="R4" s="50" t="str">
         <f>J4</f>
         <v>Värp 110</v>
       </c>
-      <c r="S4" s="64" t="str">
+      <c r="S4" s="63" t="str">
         <f t="shared" si="2"/>
         <v>Värp grön stark</v>
       </c>
-      <c r="T4" s="52" t="str">
+      <c r="T4" s="51" t="str">
         <f>L4</f>
         <v>värp grön trygg</v>
       </c>
-      <c r="V4" s="23" t="s">
-        <v>93</v>
-      </c>
-      <c r="W4" s="76" t="s">
+      <c r="V4" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="W4" s="75" t="s">
+        <v>46</v>
+      </c>
+      <c r="X4" s="76" t="s">
         <v>47</v>
       </c>
-      <c r="X4" s="77" t="s">
+      <c r="Y4" s="76" t="s">
         <v>48</v>
       </c>
-      <c r="Y4" s="77" t="s">
+      <c r="Z4" s="76" t="s">
         <v>49</v>
       </c>
-      <c r="Z4" s="77" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA4" s="78" t="s">
-        <v>94</v>
-      </c>
-      <c r="AB4" s="65" t="s">
+      <c r="AA4" s="77" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB4" s="64" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC4" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="AC4" s="66" t="s">
+      <c r="AD4" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="AD4" s="66" t="s">
+      <c r="AE4" s="65" t="s">
         <v>49</v>
       </c>
-      <c r="AE4" s="66" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF4" s="67" t="s">
-        <v>94</v>
+      <c r="AF4" s="66" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="2:33" x14ac:dyDescent="0.25">
@@ -4298,57 +4380,57 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D5">
         <v>0.86</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="23">
         <v>38.999999999999993</v>
       </c>
-      <c r="G5" s="25">
+      <c r="G5" s="24">
         <v>35.199999999999996</v>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="24">
         <v>40.199999999999996</v>
       </c>
-      <c r="I5" s="25">
+      <c r="I5" s="24">
         <v>54.3</v>
       </c>
-      <c r="J5" s="25">
+      <c r="J5" s="24">
         <v>56.7</v>
       </c>
-      <c r="K5" s="24">
+      <c r="K5" s="23">
         <v>49.9</v>
       </c>
-      <c r="L5" s="26">
+      <c r="L5" s="25">
         <v>49</v>
       </c>
-      <c r="N5" s="39">
+      <c r="N5" s="38">
         <f t="shared" ref="N5:T5" si="3">F5*$D5/F$25</f>
         <v>43.682112995233247</v>
       </c>
-      <c r="O5" s="40">
+      <c r="O5" s="39">
         <f t="shared" si="3"/>
         <v>39.526806465933717</v>
       </c>
-      <c r="P5" s="40">
+      <c r="P5" s="39">
         <f t="shared" si="3"/>
         <v>45.302303640223286</v>
       </c>
-      <c r="Q5" s="40">
+      <c r="Q5" s="39">
         <f t="shared" si="3"/>
         <v>60.43483887666622</v>
       </c>
-      <c r="R5" s="40">
+      <c r="R5" s="39">
         <f t="shared" si="3"/>
         <v>72.29355077835433</v>
       </c>
-      <c r="S5" s="39">
+      <c r="S5" s="38">
         <f t="shared" si="3"/>
         <v>58.016195973989106</v>
       </c>
-      <c r="T5" s="41">
+      <c r="T5" s="40">
         <f t="shared" si="3"/>
         <v>57.595845007858948</v>
       </c>
@@ -4357,43 +4439,43 @@
         <f>B5</f>
         <v>wheat</v>
       </c>
-      <c r="W5" s="39">
+      <c r="W5" s="38">
         <f>N5</f>
         <v>43.682112995233247</v>
       </c>
-      <c r="X5" s="40">
+      <c r="X5" s="39">
         <f>(N5+Q5)/2</f>
         <v>52.05847593594973</v>
       </c>
-      <c r="Y5" s="40">
+      <c r="Y5" s="39">
         <f>(O5+R5)/2</f>
         <v>55.910178622144024</v>
       </c>
-      <c r="Z5" s="40">
+      <c r="Z5" s="39">
         <f>(P5+R5)/2</f>
         <v>58.797927209288808</v>
       </c>
-      <c r="AA5" s="72">
+      <c r="AA5" s="71">
         <f>Z5</f>
         <v>58.797927209288808</v>
       </c>
-      <c r="AB5" s="40">
+      <c r="AB5" s="39">
         <f>W5</f>
         <v>43.682112995233247</v>
       </c>
-      <c r="AC5" s="40">
+      <c r="AC5" s="39">
         <f>S5</f>
         <v>58.016195973989106</v>
       </c>
-      <c r="AD5" s="40">
+      <c r="AD5" s="39">
         <f>(S5+T5)/2</f>
         <v>57.806020490924027</v>
       </c>
-      <c r="AE5" s="40">
+      <c r="AE5" s="39">
         <f>T5</f>
         <v>57.595845007858948</v>
       </c>
-      <c r="AF5" s="72">
+      <c r="AF5" s="71">
         <f>AE5</f>
         <v>57.595845007858948</v>
       </c>
@@ -4408,44 +4490,44 @@
       <c r="D6">
         <v>0.86</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="26">
         <v>2.4</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="27">
         <v>2.4</v>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="27">
         <v>2.4</v>
       </c>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
-      <c r="K6" s="27"/>
-      <c r="L6" s="29"/>
-      <c r="N6" s="42">
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="28"/>
+      <c r="N6" s="41">
         <f t="shared" ref="N6:N18" si="4">F6*$D6/F$25</f>
         <v>2.6881300304758931</v>
       </c>
-      <c r="O6" s="43">
+      <c r="O6" s="42">
         <f t="shared" ref="O6:O18" si="5">G6*$D6/G$25</f>
         <v>2.6950095317682083</v>
       </c>
-      <c r="P6" s="43">
+      <c r="P6" s="42">
         <f t="shared" ref="P6:P18" si="6">H6*$D6/H$25</f>
         <v>2.7046151426998981</v>
       </c>
-      <c r="Q6" s="43">
+      <c r="Q6" s="42">
         <f t="shared" ref="Q6:Q18" si="7">I6*$D6/I$25</f>
         <v>0</v>
       </c>
-      <c r="R6" s="43">
+      <c r="R6" s="42">
         <f t="shared" ref="R6:R18" si="8">J6*$D6/J$25</f>
         <v>0</v>
       </c>
-      <c r="S6" s="42">
+      <c r="S6" s="41">
         <f t="shared" ref="S6:S18" si="9">K6*$D6/K$25</f>
         <v>0</v>
       </c>
-      <c r="T6" s="44">
+      <c r="T6" s="43">
         <f t="shared" ref="T6:T18" si="10">L6*$D6/L$25</f>
         <v>0</v>
       </c>
@@ -4454,43 +4536,43 @@
         <f t="shared" ref="V6:V13" si="11">B6</f>
         <v>maize</v>
       </c>
-      <c r="W6" s="42">
+      <c r="W6" s="41">
         <f t="shared" ref="W6:W12" si="12">N6</f>
         <v>2.6881300304758931</v>
       </c>
-      <c r="X6" s="43">
+      <c r="X6" s="42">
         <f t="shared" ref="X6:X12" si="13">(N6+Q6)/2</f>
         <v>1.3440650152379465</v>
       </c>
-      <c r="Y6" s="43">
+      <c r="Y6" s="42">
         <f t="shared" ref="Y6:Y12" si="14">(O6+R6)/2</f>
         <v>1.3475047658841042</v>
       </c>
-      <c r="Z6" s="43">
+      <c r="Z6" s="42">
         <f t="shared" ref="Z6:Z12" si="15">(P6+R6)/2</f>
         <v>1.3523075713499491</v>
       </c>
-      <c r="AA6" s="73">
+      <c r="AA6" s="72">
         <f t="shared" ref="AA6:AA13" si="16">Z6</f>
         <v>1.3523075713499491</v>
       </c>
-      <c r="AB6" s="43">
+      <c r="AB6" s="42">
         <f t="shared" ref="AB6:AB17" si="17">W6</f>
         <v>2.6881300304758931</v>
       </c>
-      <c r="AC6" s="43">
+      <c r="AC6" s="42">
         <f t="shared" ref="AC6:AC12" si="18">S6</f>
         <v>0</v>
       </c>
-      <c r="AD6" s="43">
+      <c r="AD6" s="42">
         <f t="shared" ref="AD6:AD12" si="19">(S6+T6)/2</f>
         <v>0</v>
       </c>
-      <c r="AE6" s="43">
+      <c r="AE6" s="42">
         <f t="shared" ref="AE6:AE12" si="20">T6</f>
         <v>0</v>
       </c>
-      <c r="AF6" s="73">
+      <c r="AF6" s="72">
         <f t="shared" ref="AF6:AF13" si="21">AE6</f>
         <v>0</v>
       </c>
@@ -4505,50 +4587,50 @@
       <c r="D7">
         <v>0.86</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="26">
         <v>15</v>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="27">
         <v>17</v>
       </c>
-      <c r="H7" s="28">
+      <c r="H7" s="27">
         <v>15</v>
       </c>
-      <c r="I7" s="28">
+      <c r="I7" s="27">
         <v>8.1999999999999993</v>
       </c>
-      <c r="J7" s="28"/>
-      <c r="K7" s="27">
+      <c r="J7" s="27"/>
+      <c r="K7" s="26">
         <v>11.4</v>
       </c>
-      <c r="L7" s="29">
+      <c r="L7" s="28">
         <v>14.099999999999998</v>
       </c>
-      <c r="N7" s="42">
+      <c r="N7" s="41">
         <f t="shared" si="4"/>
         <v>16.800812690474331</v>
       </c>
-      <c r="O7" s="43">
+      <c r="O7" s="42">
         <f t="shared" si="5"/>
         <v>19.089650850024807</v>
       </c>
-      <c r="P7" s="43">
+      <c r="P7" s="42">
         <f t="shared" si="6"/>
         <v>16.903844641874365</v>
       </c>
-      <c r="Q7" s="43">
+      <c r="Q7" s="42">
         <f t="shared" si="7"/>
         <v>9.1264397566972946</v>
       </c>
-      <c r="R7" s="43">
+      <c r="R7" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S7" s="42">
+      <c r="S7" s="41">
         <f t="shared" si="9"/>
         <v>13.254201084237993</v>
       </c>
-      <c r="T7" s="44">
+      <c r="T7" s="43">
         <f t="shared" si="10"/>
         <v>16.573498257363489</v>
       </c>
@@ -4557,99 +4639,99 @@
         <f t="shared" si="11"/>
         <v>oats</v>
       </c>
-      <c r="W7" s="42">
+      <c r="W7" s="41">
         <f>N7</f>
         <v>16.800812690474331</v>
       </c>
-      <c r="X7" s="43">
-        <f t="shared" si="13"/>
+      <c r="X7" s="42">
+        <f>(N7+Q7)/2</f>
         <v>12.963626223585813</v>
       </c>
-      <c r="Y7" s="43">
+      <c r="Y7" s="42">
         <f t="shared" si="14"/>
         <v>9.5448254250124034</v>
       </c>
-      <c r="Z7" s="43">
+      <c r="Z7" s="42">
         <f t="shared" si="15"/>
         <v>8.4519223209371823</v>
       </c>
-      <c r="AA7" s="73">
+      <c r="AA7" s="72">
         <f t="shared" si="16"/>
         <v>8.4519223209371823</v>
       </c>
-      <c r="AB7" s="43">
+      <c r="AB7" s="42">
         <f t="shared" si="17"/>
         <v>16.800812690474331</v>
       </c>
-      <c r="AC7" s="43">
+      <c r="AC7" s="42">
         <f t="shared" si="18"/>
         <v>13.254201084237993</v>
       </c>
-      <c r="AD7" s="43">
+      <c r="AD7" s="42">
         <f t="shared" si="19"/>
         <v>14.91384967080074</v>
       </c>
-      <c r="AE7" s="43">
+      <c r="AE7" s="42">
         <f t="shared" si="20"/>
         <v>16.573498257363489</v>
       </c>
-      <c r="AF7" s="73">
+      <c r="AF7" s="72">
         <f t="shared" si="21"/>
         <v>16.573498257363489</v>
       </c>
     </row>
     <row r="8" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D8">
         <v>0.86</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="26">
         <v>3.5000000000000004</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="27">
         <v>5.7</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="27">
         <v>3.9</v>
       </c>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="27">
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="26">
         <v>4.3999999999999995</v>
       </c>
-      <c r="L8" s="29">
+      <c r="L8" s="28">
         <v>9.9</v>
       </c>
-      <c r="N8" s="42">
+      <c r="N8" s="41">
         <f t="shared" si="4"/>
         <v>3.920189627777344</v>
       </c>
-      <c r="O8" s="43">
+      <c r="O8" s="42">
         <f t="shared" si="5"/>
         <v>6.4006476379494952</v>
       </c>
-      <c r="P8" s="43">
+      <c r="P8" s="42">
         <f t="shared" si="6"/>
         <v>4.3949996068873345</v>
       </c>
-      <c r="Q8" s="43">
+      <c r="Q8" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="R8" s="43">
+      <c r="R8" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S8" s="42">
+      <c r="S8" s="41">
         <f t="shared" si="9"/>
         <v>5.1156565588286975</v>
       </c>
-      <c r="T8" s="44">
+      <c r="T8" s="43">
         <f t="shared" si="10"/>
         <v>11.636711542404154</v>
       </c>
@@ -4658,93 +4740,93 @@
         <f t="shared" si="11"/>
         <v>barley</v>
       </c>
-      <c r="W8" s="42">
+      <c r="W8" s="41">
         <f t="shared" si="12"/>
         <v>3.920189627777344</v>
       </c>
-      <c r="X8" s="43">
-        <f t="shared" si="13"/>
+      <c r="X8" s="42">
+        <f>(N8+Q8)/2</f>
         <v>1.960094813888672</v>
       </c>
-      <c r="Y8" s="43">
+      <c r="Y8" s="42">
         <f t="shared" si="14"/>
         <v>3.2003238189747476</v>
       </c>
-      <c r="Z8" s="43">
+      <c r="Z8" s="42">
         <f t="shared" si="15"/>
         <v>2.1974998034436672</v>
       </c>
-      <c r="AA8" s="73">
-        <f t="shared" si="16"/>
+      <c r="AA8" s="72">
+        <f>Z8</f>
         <v>2.1974998034436672</v>
       </c>
-      <c r="AB8" s="43">
+      <c r="AB8" s="42">
         <f t="shared" si="17"/>
         <v>3.920189627777344</v>
       </c>
-      <c r="AC8" s="43">
+      <c r="AC8" s="42">
         <f t="shared" si="18"/>
         <v>5.1156565588286975</v>
       </c>
-      <c r="AD8" s="43">
+      <c r="AD8" s="42">
         <f t="shared" si="19"/>
         <v>8.3761840506164251</v>
       </c>
-      <c r="AE8" s="43">
+      <c r="AE8" s="42">
         <f t="shared" si="20"/>
         <v>11.636711542404154</v>
       </c>
-      <c r="AF8" s="73">
+      <c r="AF8" s="72">
         <f t="shared" si="21"/>
         <v>11.636711542404154</v>
       </c>
     </row>
     <row r="9" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D9">
         <v>0.85</v>
       </c>
-      <c r="F9" s="27"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="27">
+      <c r="F9" s="26"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="26">
         <v>7.1999999999999993</v>
       </c>
-      <c r="L9" s="29">
-        <v>0</v>
-      </c>
-      <c r="N9" s="42">
+      <c r="L9" s="28">
+        <v>0</v>
+      </c>
+      <c r="N9" s="41">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O9" s="43">
+      <c r="O9" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P9" s="43">
+      <c r="P9" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q9" s="43">
+      <c r="Q9" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="R9" s="43">
+      <c r="R9" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S9" s="42">
+      <c r="S9" s="41">
         <f t="shared" si="9"/>
         <v>8.2737362949343645</v>
       </c>
-      <c r="T9" s="44">
+      <c r="T9" s="43">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
@@ -4753,43 +4835,43 @@
         <f t="shared" si="11"/>
         <v>peas</v>
       </c>
-      <c r="W9" s="42">
+      <c r="W9" s="41">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="X9" s="43">
+      <c r="X9" s="42">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Y9" s="43">
+      <c r="Y9" s="42">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="Z9" s="43">
+      <c r="Z9" s="42">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AA9" s="73">
+      <c r="AA9" s="72">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AB9" s="43">
+      <c r="AB9" s="42">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AC9" s="43">
+      <c r="AC9" s="42">
         <f t="shared" si="18"/>
         <v>8.2737362949343645</v>
       </c>
-      <c r="AD9" s="43">
+      <c r="AD9" s="42">
         <f t="shared" si="19"/>
         <v>4.1368681474671822</v>
       </c>
-      <c r="AE9" s="43">
+      <c r="AE9" s="42">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AF9" s="73">
+      <c r="AF9" s="72">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
@@ -4799,47 +4881,47 @@
         <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D10">
         <v>0.91</v>
       </c>
-      <c r="F10" s="27"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="28"/>
-      <c r="K10" s="27">
+      <c r="F10" s="26"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="26">
         <v>3</v>
       </c>
-      <c r="L10" s="29">
+      <c r="L10" s="28">
         <v>3.5000000000000004</v>
       </c>
-      <c r="N10" s="42">
+      <c r="N10" s="41">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O10" s="43">
+      <c r="O10" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P10" s="43">
+      <c r="P10" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q10" s="43">
+      <c r="Q10" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="R10" s="43">
+      <c r="R10" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S10" s="42">
+      <c r="S10" s="41">
         <f t="shared" si="9"/>
         <v>3.6907353080344469</v>
       </c>
-      <c r="T10" s="44">
+      <c r="T10" s="43">
         <f t="shared" si="10"/>
         <v>4.3531743319893401</v>
       </c>
@@ -4848,43 +4930,43 @@
         <f t="shared" si="11"/>
         <v>rapeseed</v>
       </c>
-      <c r="W10" s="42">
+      <c r="W10" s="41">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="X10" s="43">
+      <c r="X10" s="42">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Y10" s="43">
+      <c r="Y10" s="42">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="Z10" s="43">
+      <c r="Z10" s="42">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AA10" s="73">
+      <c r="AA10" s="72">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AB10" s="43">
+      <c r="AB10" s="42">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AC10" s="43">
+      <c r="AC10" s="42">
         <f t="shared" si="18"/>
         <v>3.6907353080344469</v>
       </c>
-      <c r="AD10" s="43">
+      <c r="AD10" s="42">
         <f t="shared" si="19"/>
         <v>4.021954820011894</v>
       </c>
-      <c r="AE10" s="43">
+      <c r="AE10" s="42">
         <f t="shared" si="20"/>
         <v>4.3531743319893401</v>
       </c>
-      <c r="AF10" s="73">
+      <c r="AF10" s="72">
         <f t="shared" si="21"/>
         <v>4.3531743319893401</v>
       </c>
@@ -4899,48 +4981,48 @@
       <c r="D11">
         <v>0.88</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="26">
         <v>23.599999999999998</v>
       </c>
-      <c r="G11" s="28">
+      <c r="G11" s="27">
         <v>20.7</v>
       </c>
-      <c r="H11" s="28">
+      <c r="H11" s="27">
         <v>17.299999999999997</v>
       </c>
-      <c r="I11" s="28">
+      <c r="I11" s="27">
         <v>19</v>
       </c>
-      <c r="J11" s="28">
+      <c r="J11" s="27">
         <v>15.1</v>
       </c>
-      <c r="K11" s="27"/>
-      <c r="L11" s="29"/>
-      <c r="N11" s="42">
+      <c r="K11" s="26"/>
+      <c r="L11" s="28"/>
+      <c r="N11" s="41">
         <f t="shared" si="4"/>
         <v>27.048006043083014</v>
       </c>
-      <c r="O11" s="43">
+      <c r="O11" s="42">
         <f t="shared" si="5"/>
         <v>23.785025983861281</v>
       </c>
-      <c r="P11" s="43">
+      <c r="P11" s="42">
         <f t="shared" si="6"/>
         <v>19.949157428519012</v>
       </c>
-      <c r="Q11" s="43">
+      <c r="Q11" s="42">
         <f t="shared" si="7"/>
         <v>21.638410767438849</v>
       </c>
-      <c r="R11" s="43">
+      <c r="R11" s="42">
         <f t="shared" si="8"/>
         <v>19.700518902891027</v>
       </c>
-      <c r="S11" s="42">
+      <c r="S11" s="41">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="T11" s="44">
+      <c r="T11" s="43">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
@@ -4949,93 +5031,93 @@
         <f t="shared" si="11"/>
         <v>soybean meal</v>
       </c>
-      <c r="W11" s="42">
+      <c r="W11" s="41">
         <f t="shared" si="12"/>
         <v>27.048006043083014</v>
       </c>
-      <c r="X11" s="43">
+      <c r="X11" s="42">
         <f t="shared" si="13"/>
         <v>24.343208405260931</v>
       </c>
-      <c r="Y11" s="43">
+      <c r="Y11" s="42">
         <f t="shared" si="14"/>
         <v>21.742772443376154</v>
       </c>
-      <c r="Z11" s="43">
+      <c r="Z11" s="42">
         <f t="shared" si="15"/>
         <v>19.824838165705017</v>
       </c>
-      <c r="AA11" s="73">
+      <c r="AA11" s="72">
         <f t="shared" si="16"/>
         <v>19.824838165705017</v>
       </c>
-      <c r="AB11" s="43">
+      <c r="AB11" s="42">
         <f t="shared" si="17"/>
         <v>27.048006043083014</v>
       </c>
-      <c r="AC11" s="43">
+      <c r="AC11" s="42">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AD11" s="43">
+      <c r="AD11" s="42">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AE11" s="43">
+      <c r="AE11" s="42">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AF11" s="73">
+      <c r="AF11" s="72">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D12">
         <v>0.87</v>
       </c>
-      <c r="F12" s="27"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="28"/>
-      <c r="K12" s="27">
+      <c r="F12" s="26"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="27"/>
+      <c r="K12" s="26">
         <v>2</v>
       </c>
-      <c r="L12" s="29">
+      <c r="L12" s="28">
         <v>2</v>
       </c>
-      <c r="N12" s="42">
+      <c r="N12" s="41">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O12" s="43">
+      <c r="O12" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P12" s="43">
+      <c r="P12" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q12" s="43">
+      <c r="Q12" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="R12" s="43">
+      <c r="R12" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S12" s="42">
+      <c r="S12" s="41">
         <f t="shared" si="9"/>
         <v>2.3523367897362411</v>
       </c>
-      <c r="T12" s="44">
+      <c r="T12" s="43">
         <f t="shared" si="10"/>
         <v>2.3781862912594818</v>
       </c>
@@ -5044,43 +5126,43 @@
         <f t="shared" si="11"/>
         <v>soybeans</v>
       </c>
-      <c r="W12" s="42">
+      <c r="W12" s="41">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="X12" s="43">
+      <c r="X12" s="42">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Y12" s="43">
+      <c r="Y12" s="42">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="Z12" s="43">
+      <c r="Z12" s="42">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AA12" s="73">
+      <c r="AA12" s="72">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AB12" s="43">
+      <c r="AB12" s="42">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AC12" s="43">
+      <c r="AC12" s="42">
         <f t="shared" si="18"/>
         <v>2.3523367897362411</v>
       </c>
-      <c r="AD12" s="43">
+      <c r="AD12" s="42">
         <f t="shared" si="19"/>
         <v>2.3652615404978614</v>
       </c>
-      <c r="AE12" s="43">
+      <c r="AE12" s="42">
         <f t="shared" si="20"/>
         <v>2.3781862912594818</v>
       </c>
-      <c r="AF12" s="73">
+      <c r="AF12" s="72">
         <f t="shared" si="21"/>
         <v>2.3781862912594818</v>
       </c>
@@ -5095,42 +5177,42 @@
       <c r="D13">
         <v>0.9</v>
       </c>
-      <c r="F13" s="27"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28">
+      <c r="F13" s="26"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27">
         <v>3</v>
       </c>
-      <c r="J13" s="28">
+      <c r="J13" s="27">
         <v>2</v>
       </c>
-      <c r="K13" s="27"/>
-      <c r="L13" s="29"/>
-      <c r="N13" s="42">
+      <c r="K13" s="26"/>
+      <c r="L13" s="28"/>
+      <c r="N13" s="41">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O13" s="43">
+      <c r="O13" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P13" s="43">
+      <c r="P13" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q13" s="43">
+      <c r="Q13" s="42">
         <f t="shared" si="7"/>
         <v>3.4942409732108191</v>
       </c>
-      <c r="R13" s="43">
+      <c r="R13" s="42">
         <f t="shared" si="8"/>
         <v>2.6686434395848773</v>
       </c>
-      <c r="S13" s="42">
+      <c r="S13" s="41">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="T13" s="44">
+      <c r="T13" s="43">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
@@ -5139,43 +5221,43 @@
         <f t="shared" si="11"/>
         <v>rapeseed meal</v>
       </c>
-      <c r="W13" s="42">
+      <c r="W13" s="41">
         <f>N13+N14</f>
         <v>0</v>
       </c>
-      <c r="X13" s="43">
+      <c r="X13" s="42">
         <f>(N13+Q13+N14+Q14)/2</f>
         <v>1.7471204866054095</v>
       </c>
-      <c r="Y13" s="43">
+      <c r="Y13" s="42">
         <f>(O13+R13+O14+R14)/2</f>
         <v>1.3343217197924386</v>
       </c>
-      <c r="Z13" s="43">
+      <c r="Z13" s="42">
         <f>(P13+R13+P14+R14)/2</f>
         <v>1.3343217197924386</v>
       </c>
-      <c r="AA13" s="73">
+      <c r="AA13" s="72">
         <f t="shared" si="16"/>
         <v>1.3343217197924386</v>
       </c>
-      <c r="AB13" s="43">
+      <c r="AB13" s="42">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AC13" s="43">
+      <c r="AC13" s="42">
         <f>S13+S14</f>
         <v>1.5817437034433346</v>
       </c>
-      <c r="AD13" s="43">
+      <c r="AD13" s="42">
         <f>(S13+S14+T13+T14)/2</f>
         <v>0.7908718517216673</v>
       </c>
-      <c r="AE13" s="43">
+      <c r="AE13" s="42">
         <f>T13+T14</f>
         <v>0</v>
       </c>
-      <c r="AF13" s="73">
+      <c r="AF13" s="72">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
@@ -5185,47 +5267,47 @@
         <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D14">
         <v>0.9</v>
       </c>
-      <c r="F14" s="27"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="28"/>
-      <c r="J14" s="28"/>
-      <c r="K14" s="27">
+      <c r="F14" s="26"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="26">
         <v>1.3</v>
       </c>
-      <c r="L14" s="29">
-        <v>0</v>
-      </c>
-      <c r="N14" s="42">
+      <c r="L14" s="28">
+        <v>0</v>
+      </c>
+      <c r="N14" s="41">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O14" s="43">
+      <c r="O14" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P14" s="43">
+      <c r="P14" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q14" s="43">
+      <c r="Q14" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="R14" s="43">
+      <c r="R14" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S14" s="42">
+      <c r="S14" s="41">
         <f t="shared" si="9"/>
         <v>1.5817437034433346</v>
       </c>
-      <c r="T14" s="44">
+      <c r="T14" s="43">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
@@ -5234,95 +5316,95 @@
         <f>B15</f>
         <v>wheat bran, fine</v>
       </c>
-      <c r="W14" s="42">
+      <c r="W14" s="41">
         <f>N15</f>
         <v>0</v>
       </c>
-      <c r="X14" s="43">
+      <c r="X14" s="42">
         <f>(N15+Q15)/2</f>
         <v>0</v>
       </c>
-      <c r="Y14" s="43">
+      <c r="Y14" s="42">
         <f>(O15+R15)/2</f>
         <v>1.3788420860209438</v>
       </c>
-      <c r="Z14" s="43">
+      <c r="Z14" s="42">
         <f>(P15+R15)/2</f>
         <v>2.8828262179940776</v>
       </c>
-      <c r="AA14" s="73">
+      <c r="AA14" s="72">
         <f>Z14</f>
         <v>2.8828262179940776</v>
       </c>
-      <c r="AB14" s="43">
+      <c r="AB14" s="42">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AC14" s="43">
+      <c r="AC14" s="42">
         <f>S15</f>
         <v>0</v>
       </c>
-      <c r="AD14" s="43">
+      <c r="AD14" s="42">
         <f>(S15+T15)/2</f>
         <v>0</v>
       </c>
-      <c r="AE14" s="43">
+      <c r="AE14" s="42">
         <f>T15</f>
         <v>0</v>
       </c>
-      <c r="AF14" s="73">
+      <c r="AF14" s="72">
         <f>AE14</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D15">
         <v>0.88</v>
       </c>
-      <c r="F15" s="27">
-        <v>0</v>
-      </c>
-      <c r="G15" s="28">
+      <c r="F15" s="26">
+        <v>0</v>
+      </c>
+      <c r="G15" s="27">
         <v>2.4</v>
       </c>
-      <c r="H15" s="28">
+      <c r="H15" s="27">
         <v>5</v>
       </c>
-      <c r="I15" s="28"/>
-      <c r="J15" s="28"/>
-      <c r="K15" s="27"/>
-      <c r="L15" s="29"/>
-      <c r="N15" s="42">
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="28"/>
+      <c r="N15" s="41">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O15" s="43">
+      <c r="O15" s="42">
         <f t="shared" si="5"/>
         <v>2.7576841720418876</v>
       </c>
-      <c r="P15" s="43">
+      <c r="P15" s="42">
         <f t="shared" si="6"/>
         <v>5.7656524359881551</v>
       </c>
-      <c r="Q15" s="43">
+      <c r="Q15" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="R15" s="43">
+      <c r="R15" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S15" s="42">
+      <c r="S15" s="41">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="T15" s="44">
+      <c r="T15" s="43">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
@@ -5331,43 +5413,43 @@
         <f>B16</f>
         <v>vegetable oils</v>
       </c>
-      <c r="W15" s="42">
+      <c r="W15" s="41">
         <f t="shared" ref="W15:W17" si="22">N16</f>
         <v>5.8607486129561623</v>
       </c>
-      <c r="X15" s="43">
+      <c r="X15" s="42">
         <f t="shared" ref="X15:X17" si="23">(N16+Q16)/2</f>
         <v>5.5834091194714803</v>
       </c>
-      <c r="Y15" s="43">
+      <c r="Y15" s="42">
         <f t="shared" ref="Y15:Y17" si="24">(O16+R16)/2</f>
         <v>5.5412311187951762</v>
       </c>
-      <c r="Z15" s="43">
+      <c r="Z15" s="42">
         <f t="shared" ref="Z15:Z17" si="25">(P16+R16)/2</f>
         <v>5.1583569914888532</v>
       </c>
-      <c r="AA15" s="73">
+      <c r="AA15" s="72">
         <f>Z15</f>
         <v>5.1583569914888532</v>
       </c>
-      <c r="AB15" s="43">
+      <c r="AB15" s="42">
         <f t="shared" si="17"/>
         <v>5.8607486129561623</v>
       </c>
-      <c r="AC15" s="43">
+      <c r="AC15" s="42">
         <f>S16</f>
         <v>0</v>
       </c>
-      <c r="AD15" s="43">
+      <c r="AD15" s="42">
         <f>(S16+T16)/2</f>
         <v>0</v>
       </c>
-      <c r="AE15" s="43">
+      <c r="AE15" s="42">
         <f>T16</f>
         <v>0</v>
       </c>
-      <c r="AF15" s="73">
+      <c r="AF15" s="72">
         <f>AE15</f>
         <v>0</v>
       </c>
@@ -5377,53 +5459,53 @@
         <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="26">
         <v>4.5</v>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="27">
         <v>4.3999999999999995</v>
       </c>
-      <c r="H16" s="28">
+      <c r="H16" s="27">
         <v>3.8</v>
       </c>
-      <c r="I16" s="28">
+      <c r="I16" s="27">
         <v>4.0999999999999996</v>
       </c>
-      <c r="J16" s="28">
+      <c r="J16" s="27">
         <v>3.6</v>
       </c>
-      <c r="K16" s="27"/>
-      <c r="L16" s="29"/>
-      <c r="N16" s="42">
+      <c r="K16" s="26"/>
+      <c r="L16" s="28"/>
+      <c r="N16" s="41">
         <f t="shared" si="4"/>
         <v>5.8607486129561623</v>
       </c>
-      <c r="O16" s="43">
+      <c r="O16" s="42">
         <f t="shared" si="5"/>
         <v>5.7451753584205987</v>
       </c>
-      <c r="P16" s="43">
+      <c r="P16" s="42">
         <f t="shared" si="6"/>
         <v>4.9794271038079518</v>
       </c>
-      <c r="Q16" s="43">
+      <c r="Q16" s="42">
         <f t="shared" si="7"/>
         <v>5.3060696259867983</v>
       </c>
-      <c r="R16" s="43">
+      <c r="R16" s="42">
         <f t="shared" si="8"/>
         <v>5.3372868791697545</v>
       </c>
-      <c r="S16" s="42">
+      <c r="S16" s="41">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="T16" s="44">
+      <c r="T16" s="43">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
@@ -5432,93 +5514,93 @@
         <f>B17</f>
         <v>potatoe protein</v>
       </c>
-      <c r="W16" s="42">
+      <c r="W16" s="41">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="X16" s="43">
+      <c r="X16" s="42">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="Y16" s="43">
+      <c r="Y16" s="42">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="Z16" s="43">
+      <c r="Z16" s="42">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AA16" s="73">
+      <c r="AA16" s="72">
         <f>Z16</f>
         <v>0</v>
       </c>
-      <c r="AB16" s="43">
+      <c r="AB16" s="42">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AC16" s="43">
+      <c r="AC16" s="42">
         <f>S17</f>
         <v>6.1512255133907452</v>
       </c>
-      <c r="AD16" s="43">
+      <c r="AD16" s="42">
         <f>(S17+T17)/2</f>
         <v>6.8069050412576626</v>
       </c>
-      <c r="AE16" s="43">
+      <c r="AE16" s="42">
         <f>T17</f>
         <v>7.4625845691245809</v>
       </c>
-      <c r="AF16" s="73">
+      <c r="AF16" s="72">
         <f>AE16</f>
         <v>7.4625845691245809</v>
       </c>
     </row>
     <row r="17" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D17">
         <v>0.91</v>
       </c>
-      <c r="F17" s="27"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="28"/>
-      <c r="K17" s="27">
+      <c r="F17" s="26"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="27"/>
+      <c r="K17" s="26">
         <v>5</v>
       </c>
-      <c r="L17" s="29">
+      <c r="L17" s="28">
         <v>6</v>
       </c>
-      <c r="N17" s="42">
+      <c r="N17" s="41">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O17" s="43">
+      <c r="O17" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P17" s="43">
+      <c r="P17" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q17" s="43">
+      <c r="Q17" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="R17" s="43">
+      <c r="R17" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S17" s="42">
+      <c r="S17" s="41">
         <f t="shared" si="9"/>
         <v>6.1512255133907452</v>
       </c>
-      <c r="T17" s="44">
+      <c r="T17" s="43">
         <f t="shared" si="10"/>
         <v>7.4625845691245809</v>
       </c>
@@ -5527,43 +5609,43 @@
         <f>B18</f>
         <v>maize gluten meal</v>
       </c>
-      <c r="W17" s="45">
+      <c r="W17" s="44">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="X17" s="46">
+      <c r="X17" s="45">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="Y17" s="46">
+      <c r="Y17" s="45">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="Z17" s="46">
+      <c r="Z17" s="45">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AA17" s="74">
+      <c r="AA17" s="73">
         <f>Z17</f>
         <v>0</v>
       </c>
-      <c r="AB17" s="46">
+      <c r="AB17" s="45">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AC17" s="46">
+      <c r="AC17" s="45">
         <f>S18</f>
         <v>1.5641687734050753</v>
       </c>
-      <c r="AD17" s="46">
+      <c r="AD17" s="45">
         <f>(S18+T18)/2</f>
         <v>0.78208438670253766</v>
       </c>
-      <c r="AE17" s="46">
+      <c r="AE17" s="45">
         <f>T18</f>
         <v>0</v>
       </c>
-      <c r="AF17" s="74">
+      <c r="AF17" s="73">
         <f>AE17</f>
         <v>0</v>
       </c>
@@ -5573,47 +5655,47 @@
         <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D18">
         <v>0.89</v>
       </c>
-      <c r="F18" s="27"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="28"/>
-      <c r="K18" s="27">
+      <c r="F18" s="26"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="27"/>
+      <c r="K18" s="26">
         <v>1.3</v>
       </c>
-      <c r="L18" s="29">
-        <v>0</v>
-      </c>
-      <c r="N18" s="45">
+      <c r="L18" s="28">
+        <v>0</v>
+      </c>
+      <c r="N18" s="44">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O18" s="46">
+      <c r="O18" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P18" s="46">
+      <c r="P18" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q18" s="46">
+      <c r="Q18" s="45">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="R18" s="46">
+      <c r="R18" s="45">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S18" s="45">
+      <c r="S18" s="44">
         <f t="shared" si="9"/>
         <v>1.5641687734050753</v>
       </c>
-      <c r="T18" s="47">
+      <c r="T18" s="46">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
@@ -5625,30 +5707,30 @@
         <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D19">
         <v>1</v>
       </c>
-      <c r="F19" s="27">
+      <c r="F19" s="26">
         <v>9.9</v>
       </c>
-      <c r="G19" s="28">
+      <c r="G19" s="27">
         <v>10.299999999999999</v>
       </c>
-      <c r="H19" s="28">
+      <c r="H19" s="27">
         <v>10.6</v>
       </c>
-      <c r="I19" s="28">
+      <c r="I19" s="27">
         <v>9.4</v>
       </c>
-      <c r="J19" s="28">
+      <c r="J19" s="27">
         <v>10.8</v>
       </c>
-      <c r="K19" s="27">
+      <c r="K19" s="26">
         <v>9.7000000000000011</v>
       </c>
-      <c r="L19" s="29">
+      <c r="L19" s="28">
         <v>10.7</v>
       </c>
       <c r="N19" s="4"/>
@@ -5659,46 +5741,46 @@
       <c r="S19" s="4"/>
       <c r="T19" s="4"/>
       <c r="U19" s="4"/>
-      <c r="V19" s="57" t="s">
-        <v>98</v>
-      </c>
-      <c r="W19" s="69">
+      <c r="V19" s="56" t="s">
+        <v>93</v>
+      </c>
+      <c r="W19" s="68">
         <f>(550+1650+2800)/1000/(15-0+1)*52*F24</f>
         <v>14.427074999999999</v>
       </c>
-      <c r="X19" s="70">
+      <c r="X19" s="69">
         <f>(F31+I31)/2</f>
         <v>35.955136032867976</v>
       </c>
-      <c r="Y19" s="70">
+      <c r="Y19" s="69">
         <f>(G31+J31)/2</f>
         <v>31.729574287646834</v>
       </c>
-      <c r="Z19" s="70">
+      <c r="Z19" s="69">
         <f>H31</f>
         <v>36.30498550425397</v>
       </c>
-      <c r="AA19" s="75">
+      <c r="AA19" s="74">
         <f>48/448*365.25/(1+1/12.5)</f>
         <v>36.235119047619044</v>
       </c>
-      <c r="AB19" s="69">
+      <c r="AB19" s="68">
         <f>W19</f>
         <v>14.427074999999999</v>
       </c>
-      <c r="AC19" s="70">
+      <c r="AC19" s="69">
         <f>K31</f>
         <v>31.765466750719003</v>
       </c>
-      <c r="AD19" s="70">
+      <c r="AD19" s="69">
         <f>(K31+L31)/2</f>
         <v>34.907873896644638</v>
       </c>
-      <c r="AE19" s="70">
+      <c r="AE19" s="69">
         <f>L31</f>
         <v>38.050281042570276</v>
       </c>
-      <c r="AF19" s="75">
+      <c r="AF19" s="74">
         <f>AA19</f>
         <v>36.235119047619044</v>
       </c>
@@ -5708,30 +5790,30 @@
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
-      <c r="F20" s="27">
+      <c r="F20" s="26">
         <v>1</v>
       </c>
-      <c r="G20" s="28">
+      <c r="G20" s="27">
         <v>0.70000000000000007</v>
       </c>
-      <c r="H20" s="28">
+      <c r="H20" s="27">
         <v>0.59</v>
       </c>
-      <c r="I20" s="28">
+      <c r="I20" s="27">
         <v>1</v>
       </c>
-      <c r="J20" s="28">
+      <c r="J20" s="27">
         <v>0.51</v>
       </c>
-      <c r="K20" s="27">
+      <c r="K20" s="26">
         <v>1.44</v>
       </c>
-      <c r="L20" s="29">
+      <c r="L20" s="28">
         <v>1.27</v>
       </c>
       <c r="N20" s="4"/>
@@ -5748,30 +5830,30 @@
         <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D21">
         <v>1</v>
       </c>
-      <c r="F21" s="27">
+      <c r="F21" s="26">
         <v>0.3</v>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="27">
         <v>0.3</v>
       </c>
-      <c r="H21" s="28">
+      <c r="H21" s="27">
         <v>0.3</v>
       </c>
-      <c r="I21" s="28">
+      <c r="I21" s="27">
         <v>0.2</v>
       </c>
-      <c r="J21" s="28">
+      <c r="J21" s="27">
         <v>0.2</v>
       </c>
-      <c r="K21" s="27">
+      <c r="K21" s="26">
         <v>0.3</v>
       </c>
-      <c r="L21" s="29">
+      <c r="L21" s="28">
         <v>0.3</v>
       </c>
       <c r="N21" s="4"/>
@@ -5789,30 +5871,30 @@
         <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
-      <c r="F22" s="30">
+      <c r="F22" s="29">
         <v>0.8</v>
       </c>
-      <c r="G22" s="31">
+      <c r="G22" s="30">
         <v>0.8</v>
       </c>
-      <c r="H22" s="31">
+      <c r="H22" s="30">
         <v>0.8</v>
       </c>
-      <c r="I22" s="31">
+      <c r="I22" s="30">
         <v>0.7</v>
       </c>
-      <c r="J22" s="31">
+      <c r="J22" s="30">
         <v>0.9</v>
       </c>
-      <c r="K22" s="30">
+      <c r="K22" s="29">
         <v>0.8</v>
       </c>
-      <c r="L22" s="32">
+      <c r="L22" s="31">
         <v>0.3</v>
       </c>
       <c r="N22" s="4"/>
@@ -5828,303 +5910,323 @@
       <c r="E24" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F24" s="33">
+      <c r="F24" s="32">
         <f>SUMPRODUCT(F$5:F$22/100,$D$5:$D$22)</f>
         <v>0.88781999999999994</v>
       </c>
-      <c r="G24" s="34">
+      <c r="G24" s="33">
         <f>SUMPRODUCT(G$5:G$22/100,$D$5:$D$22)</f>
         <v>0.88685999999999998</v>
       </c>
-      <c r="H24" s="34">
+      <c r="H24" s="33">
         <f>SUMPRODUCT(H$5:H$22/100,$D$5:$D$22)</f>
         <v>0.88603999999999994</v>
       </c>
-      <c r="I24" s="34">
+      <c r="I24" s="33">
         <f>SUMPRODUCT(I$5:I$22/100,$D$5:$D$22)</f>
         <v>0.88570000000000004</v>
       </c>
-      <c r="J24" s="34">
+      <c r="J24" s="33">
         <f>SUMPRODUCT(J$5:J$22/100,$D$5:$D$22)</f>
         <v>0.79860000000000009</v>
       </c>
-      <c r="K24" s="33">
+      <c r="K24" s="32">
         <f t="shared" ref="K24:L24" si="26">SUMPRODUCT(K$5:K$22/100,$D$5:$D$22)</f>
         <v>0.86208999999999991</v>
       </c>
-      <c r="L24" s="35">
+      <c r="L24" s="34">
         <f t="shared" si="26"/>
         <v>0.85735000000000006</v>
       </c>
     </row>
     <row r="25" spans="2:32" x14ac:dyDescent="0.25">
       <c r="E25" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F25" s="36">
+        <v>63</v>
+      </c>
+      <c r="F25" s="35">
         <f>SUMPRODUCT(F$5:F$18/100,$D$5:$D$18)</f>
         <v>0.76781999999999995</v>
       </c>
-      <c r="G25" s="37">
+      <c r="G25" s="36">
         <f t="shared" ref="G25:L25" si="27">SUMPRODUCT(G$5:G$18/100,$D$5:$D$18)</f>
         <v>0.76585999999999999</v>
       </c>
-      <c r="H25" s="37">
+      <c r="H25" s="36">
         <f t="shared" si="27"/>
         <v>0.76313999999999993</v>
       </c>
-      <c r="I25" s="37">
+      <c r="I25" s="36">
         <f t="shared" si="27"/>
         <v>0.77270000000000005</v>
       </c>
-      <c r="J25" s="37">
+      <c r="J25" s="36">
         <f t="shared" si="27"/>
         <v>0.6745000000000001</v>
       </c>
-      <c r="K25" s="36">
+      <c r="K25" s="35">
         <f t="shared" si="27"/>
         <v>0.73968999999999996</v>
       </c>
-      <c r="L25" s="38">
+      <c r="L25" s="37">
         <f t="shared" si="27"/>
         <v>0.73165000000000002</v>
       </c>
     </row>
     <row r="27" spans="2:32" x14ac:dyDescent="0.25">
       <c r="E27" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="F27" s="24">
+        <v>94</v>
+      </c>
+      <c r="F27" s="23">
         <v>31500</v>
       </c>
-      <c r="G27" s="34"/>
-      <c r="H27" s="34"/>
-      <c r="I27" s="25">
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="24">
         <v>12560</v>
       </c>
-      <c r="J27" s="34"/>
-      <c r="K27" s="24">
+      <c r="J27" s="33"/>
+      <c r="K27" s="23">
         <v>8300</v>
       </c>
-      <c r="L27" s="26"/>
+      <c r="L27" s="25"/>
     </row>
     <row r="28" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="E28" s="58" t="s">
-        <v>100</v>
-      </c>
-      <c r="F28" s="59" t="s">
-        <v>106</v>
-      </c>
-      <c r="G28" s="60" t="s">
+      <c r="E28" s="57" t="s">
+        <v>95</v>
+      </c>
+      <c r="F28" s="58" t="s">
         <v>101</v>
       </c>
-      <c r="H28" s="60" t="s">
+      <c r="G28" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="H28" s="59" t="s">
+        <v>97</v>
+      </c>
+      <c r="I28" s="59" t="s">
         <v>102</v>
       </c>
-      <c r="I28" s="60" t="s">
-        <v>107</v>
-      </c>
-      <c r="J28" s="60" t="s">
-        <v>108</v>
-      </c>
-      <c r="K28" s="59" t="s">
-        <v>109</v>
-      </c>
-      <c r="L28" s="61" t="s">
-        <v>110</v>
+      <c r="J28" s="59" t="s">
+        <v>103</v>
+      </c>
+      <c r="K28" s="58" t="s">
+        <v>104</v>
+      </c>
+      <c r="L28" s="60" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="2:32" x14ac:dyDescent="0.25">
       <c r="E29" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="F29" s="62">
+        <v>98</v>
+      </c>
+      <c r="F29" s="61">
         <f>(20828+279029)</f>
         <v>299857</v>
       </c>
-      <c r="G29" s="28">
+      <c r="G29" s="27">
         <v>799439</v>
       </c>
-      <c r="H29" s="28">
+      <c r="H29" s="27">
         <v>496421</v>
       </c>
-      <c r="I29" s="28">
+      <c r="I29" s="27">
         <v>221000</v>
       </c>
-      <c r="J29" s="28">
+      <c r="J29" s="27">
         <v>303200</v>
       </c>
-      <c r="K29" s="27">
+      <c r="K29" s="26">
         <v>182322</v>
       </c>
-      <c r="L29" s="29">
+      <c r="L29" s="28">
         <v>212518</v>
       </c>
     </row>
     <row r="30" spans="2:32" x14ac:dyDescent="0.25">
       <c r="E30" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="F30" s="42">
+        <v>99</v>
+      </c>
+      <c r="F30" s="41">
         <f>F29/$F$27/(28-15+1)*52</f>
         <v>35.357287981859415</v>
       </c>
-      <c r="G30" s="43">
+      <c r="G30" s="42">
         <f>G29/$F$27/(59-29+1)*52</f>
         <v>42.57125243215566</v>
       </c>
-      <c r="H30" s="43">
+      <c r="H30" s="42">
         <f>H29/$F$27/(79-60+1)*52</f>
         <v>40.974431746031748</v>
       </c>
-      <c r="I30" s="43">
+      <c r="I30" s="42">
         <f>I29/$I$27/(35-16+1)*52</f>
         <v>45.748407643312099</v>
       </c>
-      <c r="J30" s="43">
+      <c r="J30" s="42">
         <f>J29/$I$27/(74-36+1)*52</f>
         <v>32.186836518046711</v>
       </c>
-      <c r="K30" s="42">
+      <c r="K30" s="41">
         <f>K29/$K$27/(45-15+1)*52</f>
         <v>36.847042363000391</v>
       </c>
-      <c r="L30" s="44">
+      <c r="L30" s="43">
         <f>L29/$K$27/(75-46+1)*52</f>
         <v>44.381269076305216</v>
       </c>
     </row>
     <row r="31" spans="2:32" x14ac:dyDescent="0.25">
       <c r="E31" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="F31" s="45">
+        <v>100</v>
+      </c>
+      <c r="F31" s="44">
         <f>F30*F24</f>
         <v>31.390907416054425</v>
       </c>
-      <c r="G31" s="46">
+      <c r="G31" s="45">
         <f t="shared" ref="G31:J31" si="28">G30*G24</f>
         <v>37.754740931981566</v>
       </c>
-      <c r="H31" s="46">
+      <c r="H31" s="45">
         <f t="shared" si="28"/>
         <v>36.30498550425397</v>
       </c>
-      <c r="I31" s="46">
+      <c r="I31" s="45">
         <f t="shared" si="28"/>
         <v>40.519364649681528</v>
       </c>
-      <c r="J31" s="46">
+      <c r="J31" s="45">
         <f t="shared" si="28"/>
         <v>25.704407643312106</v>
       </c>
-      <c r="K31" s="45">
+      <c r="K31" s="44">
         <f t="shared" ref="K31" si="29">K30*K24</f>
         <v>31.765466750719003</v>
       </c>
-      <c r="L31" s="47">
+      <c r="L31" s="46">
         <f t="shared" ref="L31" si="30">L30*L24</f>
         <v>38.050281042570276</v>
       </c>
     </row>
     <row r="32" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
     </row>
     <row r="33" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="19"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="18"/>
+      <c r="J33" s="18"/>
     </row>
     <row r="34" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
     </row>
     <row r="35" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
     </row>
     <row r="36" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
     </row>
     <row r="37" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
     </row>
     <row r="38" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
     </row>
     <row r="39" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
     </row>
     <row r="40" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
     </row>
     <row r="41" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
     </row>
     <row r="42" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
     </row>
     <row r="43" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18"/>
     </row>
     <row r="44" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F44" s="19"/>
-      <c r="G44" s="19"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18"/>
     </row>
     <row r="45" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F45" s="19"/>
-      <c r="G45" s="19"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="18"/>
     </row>
     <row r="46" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
+      <c r="F46" s="18"/>
+      <c r="G46" s="18"/>
     </row>
     <row r="47" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="18"/>
     </row>
     <row r="48" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F48" s="19"/>
-      <c r="G48" s="19"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="18"/>
     </row>
     <row r="49" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F49" s="19"/>
-      <c r="G49" s="19"/>
+      <c r="F49" s="18"/>
+      <c r="G49" s="18"/>
     </row>
     <row r="50" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F50" s="19"/>
-      <c r="G50" s="19"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/default/LayerHerd.xlsx
+++ b/data/default/LayerHerd.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="132">
   <si>
     <t>value</t>
   </si>
@@ -453,6 +453,12 @@
   </si>
   <si>
     <t>Set to reach 10.0% for laying period</t>
+  </si>
+  <si>
+    <t>rapeseed cake</t>
+  </si>
+  <si>
+    <t>rapeseed cake for organic rations</t>
   </si>
 </sst>
 </file>
@@ -463,7 +469,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -531,6 +537,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -710,7 +723,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -854,6 +867,10 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1135,7 +1152,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q176"/>
+  <dimension ref="A1:Q177"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
@@ -1799,23 +1816,21 @@
         <v>110</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" t="s">
-        <v>46</v>
-      </c>
-      <c r="C46" t="s">
-        <v>17</v>
-      </c>
-      <c r="D46" t="s">
-        <v>112</v>
-      </c>
-      <c r="E46" s="4">
-        <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C46,'Feed rations'!$V$5:$V$17,0),MATCH(B46,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>43.682112995233247</v>
-      </c>
+    <row r="46" spans="1:8" s="90" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="88"/>
+      <c r="B46" s="88"/>
+      <c r="C46" s="88"/>
+      <c r="D46" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E46" s="13">
+        <v>0</v>
+      </c>
+      <c r="F46" s="89"/>
+      <c r="G46" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H46" s="89"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
@@ -1825,14 +1840,14 @@
         <v>46</v>
       </c>
       <c r="C47" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D47" t="s">
         <v>112</v>
       </c>
       <c r="E47" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C47,'Feed rations'!$V$5:$V$17,0),MATCH(B47,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>2.6881300304758931</v>
+        <v>43.682112995233247</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -1843,14 +1858,14 @@
         <v>46</v>
       </c>
       <c r="C48" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D48" t="s">
         <v>112</v>
       </c>
       <c r="E48" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C48,'Feed rations'!$V$5:$V$17,0),MATCH(B48,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>16.800812690474331</v>
+        <v>2.6881300304758931</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -1861,14 +1876,14 @@
         <v>46</v>
       </c>
       <c r="C49" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="D49" t="s">
         <v>112</v>
       </c>
       <c r="E49" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C49,'Feed rations'!$V$5:$V$17,0),MATCH(B49,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>3.920189627777344</v>
+        <v>16.800812690474331</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -1879,14 +1894,14 @@
         <v>46</v>
       </c>
       <c r="C50" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="D50" t="s">
         <v>112</v>
       </c>
       <c r="E50" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C50,'Feed rations'!$V$5:$V$17,0),MATCH(B50,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>3.920189627777344</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -1897,7 +1912,7 @@
         <v>46</v>
       </c>
       <c r="C51" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="D51" t="s">
         <v>112</v>
@@ -1915,14 +1930,14 @@
         <v>46</v>
       </c>
       <c r="C52" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D52" t="s">
         <v>112</v>
       </c>
       <c r="E52" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C52,'Feed rations'!$V$5:$V$17,0),MATCH(B52,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>27.048006043083014</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -1933,14 +1948,14 @@
         <v>46</v>
       </c>
       <c r="C53" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="D53" t="s">
         <v>112</v>
       </c>
       <c r="E53" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C53,'Feed rations'!$V$5:$V$17,0),MATCH(B53,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>27.048006043083014</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -1951,7 +1966,7 @@
         <v>46</v>
       </c>
       <c r="C54" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="D54" t="s">
         <v>112</v>
@@ -1969,7 +1984,7 @@
         <v>46</v>
       </c>
       <c r="C55" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="D55" t="s">
         <v>112</v>
@@ -1987,14 +2002,14 @@
         <v>46</v>
       </c>
       <c r="C56" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="D56" t="s">
         <v>112</v>
       </c>
       <c r="E56" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C56,'Feed rations'!$V$5:$V$17,0),MATCH(B56,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>5.8607486129561623</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -2005,14 +2020,14 @@
         <v>46</v>
       </c>
       <c r="C57" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="D57" t="s">
         <v>112</v>
       </c>
       <c r="E57" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C57,'Feed rations'!$V$5:$V$17,0),MATCH(B57,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>5.8607486129561623</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -2023,7 +2038,7 @@
         <v>46</v>
       </c>
       <c r="C58" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="D58" t="s">
         <v>112</v>
@@ -2038,17 +2053,17 @@
         <v>41</v>
       </c>
       <c r="B59" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C59" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D59" t="s">
         <v>112</v>
       </c>
       <c r="E59" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C59,'Feed rations'!$V$5:$V$17,0),MATCH(B59,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>52.05847593594973</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -2059,14 +2074,14 @@
         <v>47</v>
       </c>
       <c r="C60" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D60" t="s">
         <v>112</v>
       </c>
       <c r="E60" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C60,'Feed rations'!$V$5:$V$17,0),MATCH(B60,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>1.3440650152379465</v>
+        <v>52.05847593594973</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -2077,14 +2092,14 @@
         <v>47</v>
       </c>
       <c r="C61" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D61" t="s">
         <v>112</v>
       </c>
       <c r="E61" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C61,'Feed rations'!$V$5:$V$17,0),MATCH(B61,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>12.963626223585813</v>
+        <v>1.3440650152379465</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -2095,14 +2110,14 @@
         <v>47</v>
       </c>
       <c r="C62" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="D62" t="s">
         <v>112</v>
       </c>
       <c r="E62" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C62,'Feed rations'!$V$5:$V$17,0),MATCH(B62,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>1.960094813888672</v>
+        <v>12.963626223585813</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -2113,14 +2128,14 @@
         <v>47</v>
       </c>
       <c r="C63" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="D63" t="s">
         <v>112</v>
       </c>
       <c r="E63" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C63,'Feed rations'!$V$5:$V$17,0),MATCH(B63,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>1.960094813888672</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -2131,7 +2146,7 @@
         <v>47</v>
       </c>
       <c r="C64" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="D64" t="s">
         <v>112</v>
@@ -2149,14 +2164,14 @@
         <v>47</v>
       </c>
       <c r="C65" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D65" t="s">
         <v>112</v>
       </c>
       <c r="E65" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C65,'Feed rations'!$V$5:$V$17,0),MATCH(B65,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>24.343208405260931</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -2167,14 +2182,14 @@
         <v>47</v>
       </c>
       <c r="C66" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="D66" t="s">
         <v>112</v>
       </c>
       <c r="E66" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C66,'Feed rations'!$V$5:$V$17,0),MATCH(B66,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>24.343208405260931</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -2185,14 +2200,14 @@
         <v>47</v>
       </c>
       <c r="C67" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="D67" t="s">
         <v>112</v>
       </c>
       <c r="E67" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C67,'Feed rations'!$V$5:$V$17,0),MATCH(B67,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>1.7471204866054095</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -2203,14 +2218,14 @@
         <v>47</v>
       </c>
       <c r="C68" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="D68" t="s">
         <v>112</v>
       </c>
       <c r="E68" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C68,'Feed rations'!$V$5:$V$17,0),MATCH(B68,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>1.7471204866054095</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -2221,14 +2236,14 @@
         <v>47</v>
       </c>
       <c r="C69" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="D69" t="s">
         <v>112</v>
       </c>
       <c r="E69" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C69,'Feed rations'!$V$5:$V$17,0),MATCH(B69,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>5.5834091194714803</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -2239,14 +2254,14 @@
         <v>47</v>
       </c>
       <c r="C70" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="D70" t="s">
         <v>112</v>
       </c>
       <c r="E70" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C70,'Feed rations'!$V$5:$V$17,0),MATCH(B70,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>5.5834091194714803</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -2257,7 +2272,7 @@
         <v>47</v>
       </c>
       <c r="C71" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="D71" t="s">
         <v>112</v>
@@ -2272,17 +2287,17 @@
         <v>41</v>
       </c>
       <c r="B72" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C72" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D72" t="s">
         <v>112</v>
       </c>
       <c r="E72" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C72,'Feed rations'!$V$5:$V$17,0),MATCH(B72,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>55.910178622144024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -2293,14 +2308,14 @@
         <v>48</v>
       </c>
       <c r="C73" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D73" t="s">
         <v>112</v>
       </c>
       <c r="E73" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C73,'Feed rations'!$V$5:$V$17,0),MATCH(B73,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>1.3475047658841042</v>
+        <v>55.910178622144024</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -2311,14 +2326,14 @@
         <v>48</v>
       </c>
       <c r="C74" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D74" t="s">
         <v>112</v>
       </c>
       <c r="E74" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C74,'Feed rations'!$V$5:$V$17,0),MATCH(B74,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>9.5448254250124034</v>
+        <v>1.3475047658841042</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -2329,14 +2344,14 @@
         <v>48</v>
       </c>
       <c r="C75" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="D75" t="s">
         <v>112</v>
       </c>
       <c r="E75" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C75,'Feed rations'!$V$5:$V$17,0),MATCH(B75,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>3.2003238189747476</v>
+        <v>9.5448254250124034</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -2347,14 +2362,14 @@
         <v>48</v>
       </c>
       <c r="C76" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="D76" t="s">
         <v>112</v>
       </c>
       <c r="E76" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C76,'Feed rations'!$V$5:$V$17,0),MATCH(B76,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>3.2003238189747476</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -2365,7 +2380,7 @@
         <v>48</v>
       </c>
       <c r="C77" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="D77" t="s">
         <v>112</v>
@@ -2383,14 +2398,14 @@
         <v>48</v>
       </c>
       <c r="C78" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D78" t="s">
         <v>112</v>
       </c>
       <c r="E78" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C78,'Feed rations'!$V$5:$V$17,0),MATCH(B78,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>21.742772443376154</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -2401,14 +2416,14 @@
         <v>48</v>
       </c>
       <c r="C79" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="D79" t="s">
         <v>112</v>
       </c>
       <c r="E79" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C79,'Feed rations'!$V$5:$V$17,0),MATCH(B79,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>21.742772443376154</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -2419,14 +2434,14 @@
         <v>48</v>
       </c>
       <c r="C80" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="D80" t="s">
         <v>112</v>
       </c>
       <c r="E80" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C80,'Feed rations'!$V$5:$V$17,0),MATCH(B80,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>1.3343217197924386</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -2437,14 +2452,14 @@
         <v>48</v>
       </c>
       <c r="C81" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="D81" t="s">
         <v>112</v>
       </c>
       <c r="E81" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C81,'Feed rations'!$V$5:$V$17,0),MATCH(B81,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>1.3788420860209438</v>
+        <v>1.3343217197924386</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -2455,14 +2470,14 @@
         <v>48</v>
       </c>
       <c r="C82" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="D82" t="s">
         <v>112</v>
       </c>
       <c r="E82" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C82,'Feed rations'!$V$5:$V$17,0),MATCH(B82,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>5.5412311187951762</v>
+        <v>1.3788420860209438</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -2473,14 +2488,14 @@
         <v>48</v>
       </c>
       <c r="C83" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="D83" t="s">
         <v>112</v>
       </c>
       <c r="E83" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C83,'Feed rations'!$V$5:$V$17,0),MATCH(B83,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>5.5412311187951762</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -2491,7 +2506,7 @@
         <v>48</v>
       </c>
       <c r="C84" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="D84" t="s">
         <v>112</v>
@@ -2506,17 +2521,17 @@
         <v>41</v>
       </c>
       <c r="B85" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C85" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D85" t="s">
         <v>112</v>
       </c>
       <c r="E85" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C85,'Feed rations'!$V$5:$V$17,0),MATCH(B85,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>58.797927209288808</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -2527,14 +2542,14 @@
         <v>49</v>
       </c>
       <c r="C86" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D86" t="s">
         <v>112</v>
       </c>
       <c r="E86" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C86,'Feed rations'!$V$5:$V$17,0),MATCH(B86,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>1.3523075713499491</v>
+        <v>58.797927209288808</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -2545,14 +2560,14 @@
         <v>49</v>
       </c>
       <c r="C87" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D87" t="s">
         <v>112</v>
       </c>
       <c r="E87" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C87,'Feed rations'!$V$5:$V$17,0),MATCH(B87,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>8.4519223209371823</v>
+        <v>1.3523075713499491</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -2563,14 +2578,14 @@
         <v>49</v>
       </c>
       <c r="C88" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="D88" t="s">
         <v>112</v>
       </c>
       <c r="E88" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C88,'Feed rations'!$V$5:$V$17,0),MATCH(B88,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>2.1974998034436672</v>
+        <v>8.4519223209371823</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -2581,14 +2596,14 @@
         <v>49</v>
       </c>
       <c r="C89" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="D89" t="s">
         <v>112</v>
       </c>
       <c r="E89" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C89,'Feed rations'!$V$5:$V$17,0),MATCH(B89,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>2.1974998034436672</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -2599,7 +2614,7 @@
         <v>49</v>
       </c>
       <c r="C90" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="D90" t="s">
         <v>112</v>
@@ -2617,14 +2632,14 @@
         <v>49</v>
       </c>
       <c r="C91" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D91" t="s">
         <v>112</v>
       </c>
       <c r="E91" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C91,'Feed rations'!$V$5:$V$17,0),MATCH(B91,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>19.824838165705017</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -2635,14 +2650,14 @@
         <v>49</v>
       </c>
       <c r="C92" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="D92" t="s">
         <v>112</v>
       </c>
       <c r="E92" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C92,'Feed rations'!$V$5:$V$17,0),MATCH(B92,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>19.824838165705017</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -2653,14 +2668,14 @@
         <v>49</v>
       </c>
       <c r="C93" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="D93" t="s">
         <v>112</v>
       </c>
       <c r="E93" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C93,'Feed rations'!$V$5:$V$17,0),MATCH(B93,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>1.3343217197924386</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -2671,14 +2686,14 @@
         <v>49</v>
       </c>
       <c r="C94" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="D94" t="s">
         <v>112</v>
       </c>
       <c r="E94" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C94,'Feed rations'!$V$5:$V$17,0),MATCH(B94,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>2.8828262179940776</v>
+        <v>1.3343217197924386</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -2689,14 +2704,14 @@
         <v>49</v>
       </c>
       <c r="C95" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="D95" t="s">
         <v>112</v>
       </c>
       <c r="E95" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C95,'Feed rations'!$V$5:$V$17,0),MATCH(B95,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>5.1583569914888532</v>
+        <v>2.8828262179940776</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -2707,14 +2722,14 @@
         <v>49</v>
       </c>
       <c r="C96" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="D96" t="s">
         <v>112</v>
       </c>
       <c r="E96" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C96,'Feed rations'!$V$5:$V$17,0),MATCH(B96,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>5.1583569914888532</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -2725,7 +2740,7 @@
         <v>49</v>
       </c>
       <c r="C97" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="D97" t="s">
         <v>112</v>
@@ -2740,17 +2755,17 @@
         <v>41</v>
       </c>
       <c r="B98" t="s">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="C98" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D98" t="s">
         <v>112</v>
       </c>
       <c r="E98" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C98,'Feed rations'!$V$5:$V$17,0),MATCH(B98,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>58.797927209288808</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -2761,14 +2776,14 @@
         <v>89</v>
       </c>
       <c r="C99" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D99" t="s">
         <v>112</v>
       </c>
       <c r="E99" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C99,'Feed rations'!$V$5:$V$17,0),MATCH(B99,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>1.3523075713499491</v>
+        <v>58.797927209288808</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -2779,14 +2794,14 @@
         <v>89</v>
       </c>
       <c r="C100" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D100" t="s">
         <v>112</v>
       </c>
       <c r="E100" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C100,'Feed rations'!$V$5:$V$17,0),MATCH(B100,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>8.4519223209371823</v>
+        <v>1.3523075713499491</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -2797,14 +2812,14 @@
         <v>89</v>
       </c>
       <c r="C101" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="D101" t="s">
         <v>112</v>
       </c>
       <c r="E101" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C101,'Feed rations'!$V$5:$V$17,0),MATCH(B101,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>2.1974998034436672</v>
+        <v>8.4519223209371823</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -2815,14 +2830,14 @@
         <v>89</v>
       </c>
       <c r="C102" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="D102" t="s">
         <v>112</v>
       </c>
       <c r="E102" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C102,'Feed rations'!$V$5:$V$17,0),MATCH(B102,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>2.1974998034436672</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -2833,7 +2848,7 @@
         <v>89</v>
       </c>
       <c r="C103" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="D103" t="s">
         <v>112</v>
@@ -2851,14 +2866,14 @@
         <v>89</v>
       </c>
       <c r="C104" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D104" t="s">
         <v>112</v>
       </c>
       <c r="E104" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C104,'Feed rations'!$V$5:$V$17,0),MATCH(B104,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>19.824838165705017</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -2869,14 +2884,14 @@
         <v>89</v>
       </c>
       <c r="C105" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="D105" t="s">
         <v>112</v>
       </c>
       <c r="E105" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C105,'Feed rations'!$V$5:$V$17,0),MATCH(B105,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>19.824838165705017</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -2887,14 +2902,14 @@
         <v>89</v>
       </c>
       <c r="C106" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="D106" t="s">
         <v>112</v>
       </c>
       <c r="E106" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C106,'Feed rations'!$V$5:$V$17,0),MATCH(B106,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>1.3343217197924386</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -2905,14 +2920,14 @@
         <v>89</v>
       </c>
       <c r="C107" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="D107" t="s">
         <v>112</v>
       </c>
       <c r="E107" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C107,'Feed rations'!$V$5:$V$17,0),MATCH(B107,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>2.8828262179940776</v>
+        <v>1.3343217197924386</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -2923,14 +2938,14 @@
         <v>89</v>
       </c>
       <c r="C108" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="D108" t="s">
         <v>112</v>
       </c>
       <c r="E108" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C108,'Feed rations'!$V$5:$V$17,0),MATCH(B108,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>5.1583569914888532</v>
+        <v>2.8828262179940776</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -2941,14 +2956,14 @@
         <v>89</v>
       </c>
       <c r="C109" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="D109" t="s">
         <v>112</v>
       </c>
       <c r="E109" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C109,'Feed rations'!$V$5:$V$17,0),MATCH(B109,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>5.1583569914888532</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
@@ -2959,7 +2974,7 @@
         <v>89</v>
       </c>
       <c r="C110" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="D110" t="s">
         <v>112</v>
@@ -2970,27 +2985,27 @@
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E111" s="4"/>
+      <c r="A111" t="s">
+        <v>41</v>
+      </c>
+      <c r="B111" t="s">
+        <v>89</v>
+      </c>
+      <c r="C111" t="s">
+        <v>27</v>
+      </c>
+      <c r="D111" t="s">
+        <v>112</v>
+      </c>
+      <c r="E111" s="4">
+        <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C111,'Feed rations'!$V$5:$V$17,0),MATCH(B111,'Feed rations'!$W$4:$AA$4,0))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>42</v>
-      </c>
-      <c r="B112" t="s">
-        <v>46</v>
-      </c>
-      <c r="C112" t="s">
-        <v>17</v>
-      </c>
-      <c r="D112" t="s">
-        <v>112</v>
-      </c>
-      <c r="E112" s="4">
-        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C112,'Feed rations'!$V$5:$V$17,0),MATCH(B112,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>43.682112995233247</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E112" s="4"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>42</v>
       </c>
@@ -2998,17 +3013,17 @@
         <v>46</v>
       </c>
       <c r="C113" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D113" t="s">
         <v>112</v>
       </c>
       <c r="E113" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C113,'Feed rations'!$V$5:$V$17,0),MATCH(B113,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>2.6881300304758931</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+        <v>43.682112995233247</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>42</v>
       </c>
@@ -3016,17 +3031,17 @@
         <v>46</v>
       </c>
       <c r="C114" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D114" t="s">
         <v>112</v>
       </c>
       <c r="E114" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C114,'Feed rations'!$V$5:$V$17,0),MATCH(B114,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>16.800812690474331</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2.6881300304758931</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>42</v>
       </c>
@@ -3034,17 +3049,17 @@
         <v>46</v>
       </c>
       <c r="C115" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="D115" t="s">
         <v>112</v>
       </c>
       <c r="E115" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C115,'Feed rations'!$V$5:$V$17,0),MATCH(B115,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>3.920189627777344</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+        <v>16.800812690474331</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>42</v>
       </c>
@@ -3052,17 +3067,17 @@
         <v>46</v>
       </c>
       <c r="C116" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="D116" t="s">
         <v>112</v>
       </c>
       <c r="E116" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C116,'Feed rations'!$V$5:$V$17,0),MATCH(B116,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3.920189627777344</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>42</v>
       </c>
@@ -3070,7 +3085,7 @@
         <v>46</v>
       </c>
       <c r="C117" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="D117" t="s">
         <v>112</v>
@@ -3080,7 +3095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>42</v>
       </c>
@@ -3088,17 +3103,17 @@
         <v>46</v>
       </c>
       <c r="C118" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D118" t="s">
         <v>112</v>
       </c>
       <c r="E118" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C118,'Feed rations'!$V$5:$V$17,0),MATCH(B118,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>27.048006043083014</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>42</v>
       </c>
@@ -3106,17 +3121,17 @@
         <v>46</v>
       </c>
       <c r="C119" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="D119" t="s">
         <v>112</v>
       </c>
       <c r="E119" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C119,'Feed rations'!$V$5:$V$17,0),MATCH(B119,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+        <v>27.048006043083014</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>42</v>
       </c>
@@ -3124,7 +3139,7 @@
         <v>46</v>
       </c>
       <c r="C120" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="D120" t="s">
         <v>112</v>
@@ -3134,25 +3149,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>42</v>
       </c>
       <c r="B121" t="s">
         <v>46</v>
       </c>
-      <c r="C121" t="s">
-        <v>62</v>
+      <c r="C121" s="87" t="s">
+        <v>130</v>
       </c>
       <c r="D121" t="s">
         <v>112</v>
       </c>
       <c r="E121" s="4">
-        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C121,'Feed rations'!$V$5:$V$17,0),MATCH(B121,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(H121,'Feed rations'!$V$5:$V$17,0),MATCH(B121,'Feed rations'!$AB$4:$AF$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="G121" s="87" t="s">
+        <v>131</v>
+      </c>
+      <c r="H121" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>42</v>
       </c>
@@ -3160,17 +3181,17 @@
         <v>46</v>
       </c>
       <c r="C122" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="D122" t="s">
         <v>112</v>
       </c>
       <c r="E122" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C122,'Feed rations'!$V$5:$V$17,0),MATCH(B122,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>5.8607486129561623</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>42</v>
       </c>
@@ -3178,17 +3199,17 @@
         <v>46</v>
       </c>
       <c r="C123" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="D123" t="s">
         <v>112</v>
       </c>
       <c r="E123" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C123,'Feed rations'!$V$5:$V$17,0),MATCH(B123,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5.8607486129561623</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>42</v>
       </c>
@@ -3196,7 +3217,7 @@
         <v>46</v>
       </c>
       <c r="C124" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="D124" t="s">
         <v>112</v>
@@ -3206,25 +3227,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>42</v>
       </c>
       <c r="B125" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C125" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D125" t="s">
         <v>112</v>
       </c>
       <c r="E125" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C125,'Feed rations'!$V$5:$V$17,0),MATCH(B125,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>58.016195973989106</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>42</v>
       </c>
@@ -3232,17 +3253,17 @@
         <v>47</v>
       </c>
       <c r="C126" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D126" t="s">
         <v>112</v>
       </c>
       <c r="E126" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C126,'Feed rations'!$V$5:$V$17,0),MATCH(B126,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58.016195973989106</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>42</v>
       </c>
@@ -3250,17 +3271,17 @@
         <v>47</v>
       </c>
       <c r="C127" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D127" t="s">
         <v>112</v>
       </c>
       <c r="E127" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C127,'Feed rations'!$V$5:$V$17,0),MATCH(B127,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>13.254201084237993</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>42</v>
       </c>
@@ -3268,17 +3289,17 @@
         <v>47</v>
       </c>
       <c r="C128" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="D128" t="s">
         <v>112</v>
       </c>
       <c r="E128" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C128,'Feed rations'!$V$5:$V$17,0),MATCH(B128,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>5.1156565588286975</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+        <v>13.254201084237993</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>42</v>
       </c>
@@ -3286,17 +3307,17 @@
         <v>47</v>
       </c>
       <c r="C129" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="D129" t="s">
         <v>112</v>
       </c>
       <c r="E129" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C129,'Feed rations'!$V$5:$V$17,0),MATCH(B129,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>8.2737362949343645</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5.1156565588286975</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>42</v>
       </c>
@@ -3304,17 +3325,17 @@
         <v>47</v>
       </c>
       <c r="C130" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="D130" t="s">
         <v>112</v>
       </c>
       <c r="E130" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C130,'Feed rations'!$V$5:$V$17,0),MATCH(B130,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>3.6907353080344469</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+        <v>8.2737362949343645</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>42</v>
       </c>
@@ -3322,17 +3343,17 @@
         <v>47</v>
       </c>
       <c r="C131" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D131" t="s">
         <v>112</v>
       </c>
       <c r="E131" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C131,'Feed rations'!$V$5:$V$17,0),MATCH(B131,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3.6907353080344469</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>42</v>
       </c>
@@ -3340,17 +3361,17 @@
         <v>47</v>
       </c>
       <c r="C132" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="D132" t="s">
         <v>112</v>
       </c>
       <c r="E132" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C132,'Feed rations'!$V$5:$V$17,0),MATCH(B132,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>2.3523367897362411</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>42</v>
       </c>
@@ -3358,35 +3379,41 @@
         <v>47</v>
       </c>
       <c r="C133" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="D133" t="s">
         <v>112</v>
       </c>
       <c r="E133" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C133,'Feed rations'!$V$5:$V$17,0),MATCH(B133,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>1.5817437034433346</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2.3523367897362411</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>42</v>
       </c>
       <c r="B134" t="s">
         <v>47</v>
       </c>
-      <c r="C134" t="s">
-        <v>62</v>
+      <c r="C134" s="87" t="s">
+        <v>130</v>
       </c>
       <c r="D134" t="s">
         <v>112</v>
       </c>
       <c r="E134" s="4">
-        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C134,'Feed rations'!$V$5:$V$17,0),MATCH(B134,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(H134,'Feed rations'!$V$5:$V$17,0),MATCH(B134,'Feed rations'!$AB$4:$AF$4,0))</f>
+        <v>1.5817437034433346</v>
+      </c>
+      <c r="G134" s="87" t="s">
+        <v>131</v>
+      </c>
+      <c r="H134" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>42</v>
       </c>
@@ -3394,7 +3421,7 @@
         <v>47</v>
       </c>
       <c r="C135" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="D135" t="s">
         <v>112</v>
@@ -3404,7 +3431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>42</v>
       </c>
@@ -3412,17 +3439,17 @@
         <v>47</v>
       </c>
       <c r="C136" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="D136" t="s">
         <v>112</v>
       </c>
       <c r="E136" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C136,'Feed rations'!$V$5:$V$17,0),MATCH(B136,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>6.1512255133907452</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>42</v>
       </c>
@@ -3430,35 +3457,35 @@
         <v>47</v>
       </c>
       <c r="C137" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="D137" t="s">
         <v>112</v>
       </c>
       <c r="E137" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C137,'Feed rations'!$V$5:$V$17,0),MATCH(B137,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>1.5641687734050753</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6.1512255133907452</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>42</v>
       </c>
       <c r="B138" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C138" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D138" t="s">
         <v>112</v>
       </c>
       <c r="E138" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C138,'Feed rations'!$V$5:$V$17,0),MATCH(B138,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>57.806020490924027</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1.5641687734050753</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>42</v>
       </c>
@@ -3466,17 +3493,17 @@
         <v>48</v>
       </c>
       <c r="C139" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D139" t="s">
         <v>112</v>
       </c>
       <c r="E139" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C139,'Feed rations'!$V$5:$V$17,0),MATCH(B139,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+        <v>57.806020490924027</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>42</v>
       </c>
@@ -3484,17 +3511,17 @@
         <v>48</v>
       </c>
       <c r="C140" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D140" t="s">
         <v>112</v>
       </c>
       <c r="E140" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C140,'Feed rations'!$V$5:$V$17,0),MATCH(B140,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>14.91384967080074</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>42</v>
       </c>
@@ -3502,17 +3529,17 @@
         <v>48</v>
       </c>
       <c r="C141" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="D141" t="s">
         <v>112</v>
       </c>
       <c r="E141" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C141,'Feed rations'!$V$5:$V$17,0),MATCH(B141,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>8.3761840506164251</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+        <v>14.91384967080074</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>42</v>
       </c>
@@ -3520,17 +3547,17 @@
         <v>48</v>
       </c>
       <c r="C142" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="D142" t="s">
         <v>112</v>
       </c>
       <c r="E142" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C142,'Feed rations'!$V$5:$V$17,0),MATCH(B142,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>4.1368681474671822</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+        <v>8.3761840506164251</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>42</v>
       </c>
@@ -3538,17 +3565,17 @@
         <v>48</v>
       </c>
       <c r="C143" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="D143" t="s">
         <v>112</v>
       </c>
       <c r="E143" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C143,'Feed rations'!$V$5:$V$17,0),MATCH(B143,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>4.021954820011894</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+        <v>4.1368681474671822</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>42</v>
       </c>
@@ -3556,17 +3583,17 @@
         <v>48</v>
       </c>
       <c r="C144" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D144" t="s">
         <v>112</v>
       </c>
       <c r="E144" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C144,'Feed rations'!$V$5:$V$17,0),MATCH(B144,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+        <v>4.021954820011894</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>42</v>
       </c>
@@ -3574,17 +3601,17 @@
         <v>48</v>
       </c>
       <c r="C145" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="D145" t="s">
         <v>112</v>
       </c>
       <c r="E145" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C145,'Feed rations'!$V$5:$V$17,0),MATCH(B145,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>2.3652615404978614</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>42</v>
       </c>
@@ -3592,35 +3619,42 @@
         <v>48</v>
       </c>
       <c r="C146" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="D146" t="s">
         <v>112</v>
       </c>
       <c r="E146" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C146,'Feed rations'!$V$5:$V$17,0),MATCH(B146,'Feed rations'!$AB$4:$AF$4,0))</f>
+        <v>2.3652615404978614</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" s="79" t="s">
+        <v>42</v>
+      </c>
+      <c r="B147" s="79" t="s">
+        <v>48</v>
+      </c>
+      <c r="C147" s="87" t="s">
+        <v>130</v>
+      </c>
+      <c r="D147" s="79" t="s">
+        <v>112</v>
+      </c>
+      <c r="E147" s="78">
+        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(H147,'Feed rations'!$V$5:$V$17,0),MATCH(B147,'Feed rations'!$AB$4:$AF$4,0))</f>
         <v>0.7908718517216673</v>
       </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>42</v>
-      </c>
-      <c r="B147" t="s">
-        <v>48</v>
-      </c>
-      <c r="C147" t="s">
-        <v>62</v>
-      </c>
-      <c r="D147" t="s">
-        <v>112</v>
-      </c>
-      <c r="E147" s="4">
-        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C147,'Feed rations'!$V$5:$V$17,0),MATCH(B147,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F147" s="87"/>
+      <c r="G147" s="87" t="s">
+        <v>131</v>
+      </c>
+      <c r="H147" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>42</v>
       </c>
@@ -3628,7 +3662,7 @@
         <v>48</v>
       </c>
       <c r="C148" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="D148" t="s">
         <v>112</v>
@@ -3638,7 +3672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>42</v>
       </c>
@@ -3646,17 +3680,17 @@
         <v>48</v>
       </c>
       <c r="C149" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="D149" t="s">
         <v>112</v>
       </c>
       <c r="E149" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C149,'Feed rations'!$V$5:$V$17,0),MATCH(B149,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>6.8069050412576626</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>42</v>
       </c>
@@ -3664,35 +3698,35 @@
         <v>48</v>
       </c>
       <c r="C150" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="D150" t="s">
         <v>112</v>
       </c>
       <c r="E150" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C150,'Feed rations'!$V$5:$V$17,0),MATCH(B150,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0.78208438670253766</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6.8069050412576626</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>42</v>
       </c>
       <c r="B151" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C151" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D151" t="s">
         <v>112</v>
       </c>
       <c r="E151" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C151,'Feed rations'!$V$5:$V$17,0),MATCH(B151,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>57.595845007858948</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.78208438670253766</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>42</v>
       </c>
@@ -3700,17 +3734,17 @@
         <v>49</v>
       </c>
       <c r="C152" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D152" t="s">
         <v>112</v>
       </c>
       <c r="E152" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C152,'Feed rations'!$V$5:$V$17,0),MATCH(B152,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+        <v>57.595845007858948</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>42</v>
       </c>
@@ -3718,17 +3752,17 @@
         <v>49</v>
       </c>
       <c r="C153" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D153" t="s">
         <v>112</v>
       </c>
       <c r="E153" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C153,'Feed rations'!$V$5:$V$17,0),MATCH(B153,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>16.573498257363489</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>42</v>
       </c>
@@ -3736,17 +3770,17 @@
         <v>49</v>
       </c>
       <c r="C154" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="D154" t="s">
         <v>112</v>
       </c>
       <c r="E154" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C154,'Feed rations'!$V$5:$V$17,0),MATCH(B154,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>11.636711542404154</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+        <v>16.573498257363489</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>42</v>
       </c>
@@ -3754,17 +3788,17 @@
         <v>49</v>
       </c>
       <c r="C155" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="D155" t="s">
         <v>112</v>
       </c>
       <c r="E155" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C155,'Feed rations'!$V$5:$V$17,0),MATCH(B155,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+        <v>11.636711542404154</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>42</v>
       </c>
@@ -3772,17 +3806,17 @@
         <v>49</v>
       </c>
       <c r="C156" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="D156" t="s">
         <v>112</v>
       </c>
       <c r="E156" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C156,'Feed rations'!$V$5:$V$17,0),MATCH(B156,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>4.3531743319893401</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>42</v>
       </c>
@@ -3790,17 +3824,17 @@
         <v>49</v>
       </c>
       <c r="C157" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D157" t="s">
         <v>112</v>
       </c>
       <c r="E157" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C157,'Feed rations'!$V$5:$V$17,0),MATCH(B157,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+        <v>4.3531743319893401</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>42</v>
       </c>
@@ -3808,17 +3842,17 @@
         <v>49</v>
       </c>
       <c r="C158" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="D158" t="s">
         <v>112</v>
       </c>
       <c r="E158" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C158,'Feed rations'!$V$5:$V$17,0),MATCH(B158,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>2.3781862912594818</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>42</v>
       </c>
@@ -3826,35 +3860,41 @@
         <v>49</v>
       </c>
       <c r="C159" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="D159" t="s">
         <v>112</v>
       </c>
       <c r="E159" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C159,'Feed rations'!$V$5:$V$17,0),MATCH(B159,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2.3781862912594818</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>42</v>
       </c>
       <c r="B160" t="s">
         <v>49</v>
       </c>
-      <c r="C160" t="s">
-        <v>62</v>
+      <c r="C160" s="87" t="s">
+        <v>130</v>
       </c>
       <c r="D160" t="s">
         <v>112</v>
       </c>
       <c r="E160" s="4">
-        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C160,'Feed rations'!$V$5:$V$17,0),MATCH(B160,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(H160,'Feed rations'!$V$5:$V$17,0),MATCH(B160,'Feed rations'!$AB$4:$AF$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="G160" s="87" t="s">
+        <v>131</v>
+      </c>
+      <c r="H160" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>42</v>
       </c>
@@ -3862,7 +3902,7 @@
         <v>49</v>
       </c>
       <c r="C161" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="D161" t="s">
         <v>112</v>
@@ -3872,7 +3912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>42</v>
       </c>
@@ -3880,17 +3920,17 @@
         <v>49</v>
       </c>
       <c r="C162" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="D162" t="s">
         <v>112</v>
       </c>
       <c r="E162" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C162,'Feed rations'!$V$5:$V$17,0),MATCH(B162,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>7.4625845691245809</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>42</v>
       </c>
@@ -3898,35 +3938,35 @@
         <v>49</v>
       </c>
       <c r="C163" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="D163" t="s">
         <v>112</v>
       </c>
       <c r="E163" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C163,'Feed rations'!$V$5:$V$17,0),MATCH(B163,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7.4625845691245809</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>42</v>
       </c>
       <c r="B164" t="s">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="C164" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D164" t="s">
         <v>112</v>
       </c>
       <c r="E164" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C164,'Feed rations'!$V$5:$V$17,0),MATCH(B164,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>57.595845007858948</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>42</v>
       </c>
@@ -3934,17 +3974,17 @@
         <v>89</v>
       </c>
       <c r="C165" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D165" t="s">
         <v>112</v>
       </c>
       <c r="E165" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C165,'Feed rations'!$V$5:$V$17,0),MATCH(B165,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+        <v>57.595845007858948</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>42</v>
       </c>
@@ -3952,17 +3992,17 @@
         <v>89</v>
       </c>
       <c r="C166" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D166" t="s">
         <v>112</v>
       </c>
       <c r="E166" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C166,'Feed rations'!$V$5:$V$17,0),MATCH(B166,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>16.573498257363489</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>42</v>
       </c>
@@ -3970,17 +4010,17 @@
         <v>89</v>
       </c>
       <c r="C167" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="D167" t="s">
         <v>112</v>
       </c>
       <c r="E167" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C167,'Feed rations'!$V$5:$V$17,0),MATCH(B167,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>11.636711542404154</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+        <v>16.573498257363489</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>42</v>
       </c>
@@ -3988,17 +4028,17 @@
         <v>89</v>
       </c>
       <c r="C168" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="D168" t="s">
         <v>112</v>
       </c>
       <c r="E168" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C168,'Feed rations'!$V$5:$V$17,0),MATCH(B168,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+        <v>11.636711542404154</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>42</v>
       </c>
@@ -4006,17 +4046,17 @@
         <v>89</v>
       </c>
       <c r="C169" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="D169" t="s">
         <v>112</v>
       </c>
       <c r="E169" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C169,'Feed rations'!$V$5:$V$17,0),MATCH(B169,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>4.3531743319893401</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>42</v>
       </c>
@@ -4024,17 +4064,17 @@
         <v>89</v>
       </c>
       <c r="C170" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D170" t="s">
         <v>112</v>
       </c>
       <c r="E170" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C170,'Feed rations'!$V$5:$V$17,0),MATCH(B170,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+        <v>4.3531743319893401</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>42</v>
       </c>
@@ -4042,17 +4082,17 @@
         <v>89</v>
       </c>
       <c r="C171" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="D171" t="s">
         <v>112</v>
       </c>
       <c r="E171" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C171,'Feed rations'!$V$5:$V$17,0),MATCH(B171,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>2.3781862912594818</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>42</v>
       </c>
@@ -4060,35 +4100,41 @@
         <v>89</v>
       </c>
       <c r="C172" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="D172" t="s">
         <v>112</v>
       </c>
       <c r="E172" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C172,'Feed rations'!$V$5:$V$17,0),MATCH(B172,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2.3781862912594818</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>42</v>
       </c>
       <c r="B173" t="s">
         <v>89</v>
       </c>
-      <c r="C173" t="s">
-        <v>62</v>
+      <c r="C173" s="87" t="s">
+        <v>130</v>
       </c>
       <c r="D173" t="s">
         <v>112</v>
       </c>
       <c r="E173" s="4">
-        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C173,'Feed rations'!$V$5:$V$17,0),MATCH(B173,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(H173,'Feed rations'!$V$5:$V$17,0),MATCH(B173,'Feed rations'!$AB$4:$AF$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="G173" s="87" t="s">
+        <v>131</v>
+      </c>
+      <c r="H173" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>42</v>
       </c>
@@ -4096,7 +4142,7 @@
         <v>89</v>
       </c>
       <c r="C174" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="D174" t="s">
         <v>112</v>
@@ -4106,7 +4152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>42</v>
       </c>
@@ -4114,17 +4160,17 @@
         <v>89</v>
       </c>
       <c r="C175" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="D175" t="s">
         <v>112</v>
       </c>
       <c r="E175" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C175,'Feed rations'!$V$5:$V$17,0),MATCH(B175,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>7.4625845691245809</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>42</v>
       </c>
@@ -4132,13 +4178,31 @@
         <v>89</v>
       </c>
       <c r="C176" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="D176" t="s">
         <v>112</v>
       </c>
       <c r="E176" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C176,'Feed rations'!$V$5:$V$17,0),MATCH(B176,'Feed rations'!$AB$4:$AF$4,0))</f>
+        <v>7.4625845691245809</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>42</v>
+      </c>
+      <c r="B177" t="s">
+        <v>89</v>
+      </c>
+      <c r="C177" t="s">
+        <v>27</v>
+      </c>
+      <c r="D177" t="s">
+        <v>112</v>
+      </c>
+      <c r="E177" s="4">
+        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C177,'Feed rations'!$V$5:$V$17,0),MATCH(B177,'Feed rations'!$AB$4:$AF$4,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -4557,7 +4621,7 @@
         <v>1.3523075713499491</v>
       </c>
       <c r="AB6" s="42">
-        <f t="shared" ref="AB6:AB17" si="17">W6</f>
+        <f t="shared" ref="AB6:AB13" si="17">W6</f>
         <v>2.6881300304758931</v>
       </c>
       <c r="AC6" s="42">
@@ -5321,11 +5385,11 @@
         <v>0</v>
       </c>
       <c r="X14" s="42">
-        <f>(N15+Q15)/2</f>
+        <f t="shared" ref="X14:Y17" si="22">(N15+Q15)/2</f>
         <v>0</v>
       </c>
       <c r="Y14" s="42">
-        <f>(O15+R15)/2</f>
+        <f t="shared" si="22"/>
         <v>1.3788420860209438</v>
       </c>
       <c r="Z14" s="42">
@@ -5337,7 +5401,7 @@
         <v>2.8828262179940776</v>
       </c>
       <c r="AB14" s="42">
-        <f t="shared" si="17"/>
+        <f>W14</f>
         <v>0</v>
       </c>
       <c r="AC14" s="42">
@@ -5414,19 +5478,19 @@
         <v>vegetable oils</v>
       </c>
       <c r="W15" s="41">
-        <f t="shared" ref="W15:W17" si="22">N16</f>
+        <f>N16</f>
         <v>5.8607486129561623</v>
       </c>
       <c r="X15" s="42">
-        <f t="shared" ref="X15:X17" si="23">(N16+Q16)/2</f>
+        <f t="shared" si="22"/>
         <v>5.5834091194714803</v>
       </c>
       <c r="Y15" s="42">
-        <f t="shared" ref="Y15:Y17" si="24">(O16+R16)/2</f>
+        <f t="shared" si="22"/>
         <v>5.5412311187951762</v>
       </c>
       <c r="Z15" s="42">
-        <f t="shared" ref="Z15:Z17" si="25">(P16+R16)/2</f>
+        <f>(P16+R16)/2</f>
         <v>5.1583569914888532</v>
       </c>
       <c r="AA15" s="72">
@@ -5434,7 +5498,7 @@
         <v>5.1583569914888532</v>
       </c>
       <c r="AB15" s="42">
-        <f t="shared" si="17"/>
+        <f>W15</f>
         <v>5.8607486129561623</v>
       </c>
       <c r="AC15" s="42">
@@ -5515,19 +5579,19 @@
         <v>potatoe protein</v>
       </c>
       <c r="W16" s="41">
+        <f>N17</f>
+        <v>0</v>
+      </c>
+      <c r="X16" s="42">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="X16" s="42">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
       <c r="Y16" s="42">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Z16" s="42">
-        <f t="shared" si="25"/>
+        <f>(P17+R17)/2</f>
         <v>0</v>
       </c>
       <c r="AA16" s="72">
@@ -5535,7 +5599,7 @@
         <v>0</v>
       </c>
       <c r="AB16" s="42">
-        <f t="shared" si="17"/>
+        <f>W16</f>
         <v>0</v>
       </c>
       <c r="AC16" s="42">
@@ -5610,19 +5674,19 @@
         <v>maize gluten meal</v>
       </c>
       <c r="W17" s="44">
+        <f>N18</f>
+        <v>0</v>
+      </c>
+      <c r="X17" s="45">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="X17" s="45">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
       <c r="Y17" s="45">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Z17" s="45">
-        <f t="shared" si="25"/>
+        <f>(P18+R18)/2</f>
         <v>0</v>
       </c>
       <c r="AA17" s="73">
@@ -5630,7 +5694,7 @@
         <v>0</v>
       </c>
       <c r="AB17" s="45">
-        <f t="shared" si="17"/>
+        <f>W17</f>
         <v>0</v>
       </c>
       <c r="AC17" s="45">
@@ -5931,11 +5995,11 @@
         <v>0.79860000000000009</v>
       </c>
       <c r="K24" s="32">
-        <f t="shared" ref="K24:L24" si="26">SUMPRODUCT(K$5:K$22/100,$D$5:$D$22)</f>
+        <f t="shared" ref="K24:L24" si="23">SUMPRODUCT(K$5:K$22/100,$D$5:$D$22)</f>
         <v>0.86208999999999991</v>
       </c>
       <c r="L24" s="34">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0.85735000000000006</v>
       </c>
     </row>
@@ -5948,27 +6012,27 @@
         <v>0.76781999999999995</v>
       </c>
       <c r="G25" s="36">
-        <f t="shared" ref="G25:L25" si="27">SUMPRODUCT(G$5:G$18/100,$D$5:$D$18)</f>
+        <f t="shared" ref="G25:L25" si="24">SUMPRODUCT(G$5:G$18/100,$D$5:$D$18)</f>
         <v>0.76585999999999999</v>
       </c>
       <c r="H25" s="36">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>0.76313999999999993</v>
       </c>
       <c r="I25" s="36">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>0.77270000000000005</v>
       </c>
       <c r="J25" s="36">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>0.6745000000000001</v>
       </c>
       <c r="K25" s="35">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>0.73968999999999996</v>
       </c>
       <c r="L25" s="37">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>0.73165000000000002</v>
       </c>
     </row>
@@ -6085,27 +6149,27 @@
         <v>31.390907416054425</v>
       </c>
       <c r="G31" s="45">
-        <f t="shared" ref="G31:J31" si="28">G30*G24</f>
+        <f t="shared" ref="G31:J31" si="25">G30*G24</f>
         <v>37.754740931981566</v>
       </c>
       <c r="H31" s="45">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>36.30498550425397</v>
       </c>
       <c r="I31" s="45">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>40.519364649681528</v>
       </c>
       <c r="J31" s="45">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>25.704407643312106</v>
       </c>
       <c r="K31" s="44">
-        <f t="shared" ref="K31" si="29">K30*K24</f>
+        <f t="shared" ref="K31" si="26">K30*K24</f>
         <v>31.765466750719003</v>
       </c>
       <c r="L31" s="46">
-        <f t="shared" ref="L31" si="30">L30*L24</f>
+        <f t="shared" ref="L31" si="27">L30*L24</f>
         <v>38.050281042570276</v>
       </c>
     </row>

--- a/data/default/LayerHerd.xlsx
+++ b/data/default/LayerHerd.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="136">
   <si>
     <t>value</t>
   </si>
@@ -404,9 +404,6 @@
     <t>share_in_ration</t>
   </si>
   <si>
-    <t>Creates problems with too much poultry meat</t>
-  </si>
-  <si>
     <t>Slaughter and live weights</t>
   </si>
   <si>
@@ -437,9 +434,6 @@
     <t>% of slaughtered</t>
   </si>
   <si>
-    <t>assumption. 2.3% for broilers</t>
-  </si>
-  <si>
     <t>Set to reach 5.0% for laying period. Avg gård A and B</t>
   </si>
   <si>
@@ -459,6 +453,24 @@
   </si>
   <si>
     <t>rapeseed cake for organic rations</t>
+  </si>
+  <si>
+    <t>5 mil. hatched, 0.5 mil dead during prod., 2.9 mil food, 0.6 mil pet food, 1.4 mil to destruction at slaughter</t>
+  </si>
+  <si>
+    <t>average_live_weight</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>https://lohmann-breeders.com/lohmanninfo/management-tools-to-influence-egg-weight-in-commercial-layers/</t>
+  </si>
+  <si>
+    <t>assumption to avoid too much organic poultry meat</t>
+  </si>
+  <si>
+    <t>SJV 2016-2020</t>
   </si>
 </sst>
 </file>
@@ -469,7 +481,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -544,6 +556,14 @@
     <font>
       <sz val="11"/>
       <color theme="7"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -719,11 +739,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -871,8 +892,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -1152,7 +1176,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q177"/>
+  <dimension ref="A1:Q180"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
@@ -1246,10 +1270,10 @@
         <v>4</v>
       </c>
       <c r="G5" s="79" t="s">
+        <v>118</v>
+      </c>
+      <c r="H5" t="s">
         <v>119</v>
-      </c>
-      <c r="H5" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -1318,7 +1342,7 @@
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="E11" s="4"/>
       <c r="M11" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -1335,13 +1359,13 @@
         <v>2</v>
       </c>
       <c r="F12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G12" s="79" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M12" s="80" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N12" s="81"/>
       <c r="O12" s="81"/>
@@ -1366,13 +1390,13 @@
         <v>2</v>
       </c>
       <c r="F13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G13" s="79" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M13" s="83" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="N13" s="84"/>
       <c r="O13" s="84"/>
@@ -1395,10 +1419,10 @@
         <v>1.7</v>
       </c>
       <c r="F14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G14" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H14" t="s">
         <v>43</v>
@@ -1415,82 +1439,80 @@
         <v>3.45</v>
       </c>
       <c r="F15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H15" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>41</v>
+      </c>
       <c r="D16" t="s">
         <v>5</v>
       </c>
-      <c r="E16" s="78">
+      <c r="E16" s="91">
+        <v>48</v>
+      </c>
+      <c r="F16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G16" s="79" t="s">
+        <v>130</v>
+      </c>
+      <c r="H16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" t="s">
         <v>5</v>
       </c>
-      <c r="F16" t="s">
-        <v>123</v>
-      </c>
-      <c r="G16" s="79" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E17" s="4"/>
+      <c r="E17" s="91">
+        <v>100</v>
+      </c>
+      <c r="F17" t="s">
+        <v>122</v>
+      </c>
+      <c r="G17" s="79" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="15"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="10"/>
-      <c r="D19" s="7" t="s">
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="15"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="10"/>
+      <c r="D20" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="13">
-        <v>0</v>
-      </c>
-      <c r="F19" s="7" t="s">
+      <c r="E20" s="13">
+        <v>0</v>
+      </c>
+      <c r="F20" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G20" s="7" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20" s="8"/>
-      <c r="D20" t="s">
-        <v>40</v>
-      </c>
-      <c r="E20" s="11">
-        <f>(22.5/64*52+20.2/58*52)/2</f>
-        <v>18.195797413793102</v>
-      </c>
-      <c r="F20" t="s">
-        <v>51</v>
-      </c>
-      <c r="G20" t="s">
-        <v>52</v>
-      </c>
-      <c r="H20" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1498,19 +1520,24 @@
         <v>41</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="14">
-        <f>E20</f>
+      <c r="E21" s="11">
+        <f>(22.5/64*52+20.2/58*52)/2</f>
         <v>18.195797413793102</v>
       </c>
-      <c r="F21" s="14" t="str">
-        <f>F20</f>
-        <v>kg/head/year</v>
+      <c r="F21" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21" t="s">
+        <v>52</v>
+      </c>
+      <c r="H21" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1518,14 +1545,14 @@
         <v>41</v>
       </c>
       <c r="B22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" t="s">
         <v>40</v>
       </c>
       <c r="E22" s="14">
-        <f>E20</f>
+        <f>E21</f>
         <v>18.195797413793102</v>
       </c>
       <c r="F22" s="14" t="str">
@@ -1535,24 +1562,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="11">
-        <f>20/60*52</f>
-        <v>17.333333333333332</v>
-      </c>
-      <c r="F23" t="s">
-        <v>51</v>
-      </c>
-      <c r="H23" t="s">
-        <v>44</v>
+      <c r="E23" s="14">
+        <f>E21</f>
+        <v>18.195797413793102</v>
+      </c>
+      <c r="F23" s="14" t="str">
+        <f>F22</f>
+        <v>kg/head/year</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1560,19 +1585,21 @@
         <v>42</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" t="s">
         <v>40</v>
       </c>
-      <c r="E24" s="14">
-        <f>E23</f>
+      <c r="E24" s="11">
+        <f>20/60*52</f>
         <v>17.333333333333332</v>
       </c>
-      <c r="F24" s="14" t="str">
-        <f>F23</f>
-        <v>kg/head/year</v>
+      <c r="F24" t="s">
+        <v>51</v>
+      </c>
+      <c r="H24" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1580,14 +1607,14 @@
         <v>42</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" t="s">
         <v>40</v>
       </c>
       <c r="E25" s="14">
-        <f>E23</f>
+        <f>E24</f>
         <v>17.333333333333332</v>
       </c>
       <c r="F25" s="14" t="str">
@@ -1596,103 +1623,118 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" t="s">
+        <v>49</v>
+      </c>
       <c r="C26" s="8"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
+      <c r="D26" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26" s="14">
+        <f>E24</f>
+        <v>17.333333333333332</v>
+      </c>
+      <c r="F26" s="14" t="str">
+        <f>F25</f>
+        <v>kg/head/year</v>
+      </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
+      <c r="C27" s="8"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D28" t="s">
+      <c r="A28" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" t="s">
+        <v>131</v>
+      </c>
+      <c r="E29">
+        <f>1.2/2</f>
+        <v>0.6</v>
+      </c>
+      <c r="F29" t="s">
+        <v>132</v>
+      </c>
+      <c r="H29" s="92" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D30" t="s">
+        <v>131</v>
+      </c>
+      <c r="E30">
+        <v>1.4</v>
+      </c>
+      <c r="F30" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
+        <v>131</v>
+      </c>
+      <c r="E31">
+        <v>1.6</v>
+      </c>
+      <c r="F31" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E32" s="8"/>
+      <c r="G32" s="8"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
         <v>14</v>
       </c>
-      <c r="E28" s="8">
-        <v>0</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="E33" s="79">
+        <v>1.17</v>
+      </c>
+      <c r="F33" t="s">
         <v>15</v>
       </c>
-      <c r="G28" s="8" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E29" s="8"/>
-      <c r="G29" s="8"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E30" s="8"/>
-      <c r="G30" s="8"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
+      <c r="G33" s="8"/>
+      <c r="H33" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="70" t="s">
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="70" t="s">
         <v>107</v>
       </c>
-      <c r="G32" s="6"/>
-      <c r="H32" s="70" t="s">
+      <c r="G35" s="6"/>
+      <c r="H35" s="70" t="s">
         <v>110</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" t="s">
-        <v>46</v>
-      </c>
-      <c r="D33" t="s">
-        <v>111</v>
-      </c>
-      <c r="E33" s="4">
-        <f>INDEX('Feed rations'!$W$19:$AA$19,MATCH(B33,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>14.427074999999999</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" t="s">
-        <v>47</v>
-      </c>
-      <c r="D34" t="s">
-        <v>111</v>
-      </c>
-      <c r="E34" s="4">
-        <f>INDEX('Feed rations'!$W$19:$AA$19,MATCH(B34,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>35.955136032867976</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" t="s">
-        <v>48</v>
-      </c>
-      <c r="D35" t="s">
-        <v>111</v>
-      </c>
-      <c r="E35" s="4">
-        <f>INDEX('Feed rations'!$W$19:$AA$19,MATCH(B35,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>31.729574287646834</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -1700,14 +1742,14 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D36" t="s">
         <v>111</v>
       </c>
       <c r="E36" s="4">
         <f>INDEX('Feed rations'!$W$19:$AA$19,MATCH(B36,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>36.30498550425397</v>
+        <v>14.427074999999999</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -1715,59 +1757,59 @@
         <v>41</v>
       </c>
       <c r="B37" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="D37" t="s">
         <v>111</v>
       </c>
       <c r="E37" s="4">
         <f>INDEX('Feed rations'!$W$19:$AA$19,MATCH(B37,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>36.235119047619044</v>
+        <v>35.955136032867976</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" t="s">
+        <v>48</v>
+      </c>
+      <c r="D38" t="s">
+        <v>111</v>
+      </c>
+      <c r="E38" s="4">
+        <f>INDEX('Feed rations'!$W$19:$AA$19,MATCH(B38,'Feed rations'!$W$4:$AA$4,0))</f>
+        <v>31.729574287646834</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D39" t="s">
         <v>111</v>
       </c>
       <c r="E39" s="4">
-        <f>INDEX('Feed rations'!$AB$19:$AF$19,MATCH(B39,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>14.427074999999999</v>
+        <f>INDEX('Feed rations'!$W$19:$AA$19,MATCH(B39,'Feed rations'!$W$4:$AA$4,0))</f>
+        <v>36.30498550425397</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="D40" t="s">
         <v>111</v>
       </c>
       <c r="E40" s="4">
-        <f>INDEX('Feed rations'!$AB$19:$AF$19,MATCH(B40,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>31.765466750719003</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" t="s">
-        <v>48</v>
-      </c>
-      <c r="D41" t="s">
-        <v>111</v>
-      </c>
-      <c r="E41" s="4">
-        <f>INDEX('Feed rations'!$AB$19:$AF$19,MATCH(B41,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>34.907873896644638</v>
+        <f>INDEX('Feed rations'!$W$19:$AA$19,MATCH(B40,'Feed rations'!$W$4:$AA$4,0))</f>
+        <v>36.235119047619044</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -1775,14 +1817,14 @@
         <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D42" t="s">
         <v>111</v>
       </c>
       <c r="E42" s="4">
         <f>INDEX('Feed rations'!$AB$19:$AF$19,MATCH(B42,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>38.050281042570276</v>
+        <v>14.427074999999999</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -1790,103 +1832,94 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="D43" t="s">
         <v>111</v>
       </c>
       <c r="E43" s="4">
         <f>INDEX('Feed rations'!$AB$19:$AF$19,MATCH(B43,'Feed rations'!$AB$4:$AF$4,0))</f>
+        <v>31.765466750719003</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" t="s">
+        <v>48</v>
+      </c>
+      <c r="D44" t="s">
+        <v>111</v>
+      </c>
+      <c r="E44" s="4">
+        <f>INDEX('Feed rations'!$AB$19:$AF$19,MATCH(B44,'Feed rations'!$AB$4:$AF$4,0))</f>
+        <v>34.907873896644638</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" t="s">
+        <v>49</v>
+      </c>
+      <c r="D45" t="s">
+        <v>111</v>
+      </c>
+      <c r="E45" s="4">
+        <f>INDEX('Feed rations'!$AB$19:$AF$19,MATCH(B45,'Feed rations'!$AB$4:$AF$4,0))</f>
+        <v>38.050281042570276</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>42</v>
+      </c>
+      <c r="B46" t="s">
+        <v>89</v>
+      </c>
+      <c r="D46" t="s">
+        <v>111</v>
+      </c>
+      <c r="E46" s="4">
+        <f>INDEX('Feed rations'!$AB$19:$AF$19,MATCH(B46,'Feed rations'!$AB$4:$AF$4,0))</f>
         <v>36.235119047619044</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="6" t="s">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="70" t="s">
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="70" t="s">
         <v>109</v>
       </c>
-      <c r="G45" s="6"/>
-      <c r="H45" s="70" t="s">
+      <c r="G48" s="6"/>
+      <c r="H48" s="70" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="46" spans="1:8" s="90" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="88"/>
-      <c r="B46" s="88"/>
-      <c r="C46" s="88"/>
-      <c r="D46" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="E46" s="13">
-        <v>0</v>
-      </c>
-      <c r="F46" s="89"/>
-      <c r="G46" s="7" t="s">
+    <row r="49" spans="1:8" s="90" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="88"/>
+      <c r="B49" s="88"/>
+      <c r="C49" s="88"/>
+      <c r="D49" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E49" s="13">
+        <v>0</v>
+      </c>
+      <c r="F49" s="89"/>
+      <c r="G49" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="H46" s="89"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" t="s">
-        <v>46</v>
-      </c>
-      <c r="C47" t="s">
-        <v>17</v>
-      </c>
-      <c r="D47" t="s">
-        <v>112</v>
-      </c>
-      <c r="E47" s="4">
-        <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C47,'Feed rations'!$V$5:$V$17,0),MATCH(B47,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>43.682112995233247</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" t="s">
-        <v>46</v>
-      </c>
-      <c r="C48" t="s">
-        <v>19</v>
-      </c>
-      <c r="D48" t="s">
-        <v>112</v>
-      </c>
-      <c r="E48" s="4">
-        <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C48,'Feed rations'!$V$5:$V$17,0),MATCH(B48,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>2.6881300304758931</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" t="s">
-        <v>46</v>
-      </c>
-      <c r="C49" t="s">
-        <v>18</v>
-      </c>
-      <c r="D49" t="s">
-        <v>112</v>
-      </c>
-      <c r="E49" s="4">
-        <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C49,'Feed rations'!$V$5:$V$17,0),MATCH(B49,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>16.800812690474331</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H49" s="89"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>41</v>
       </c>
@@ -1894,17 +1927,17 @@
         <v>46</v>
       </c>
       <c r="C50" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="D50" t="s">
         <v>112</v>
       </c>
       <c r="E50" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C50,'Feed rations'!$V$5:$V$17,0),MATCH(B50,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>3.920189627777344</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>43.682112995233247</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>41</v>
       </c>
@@ -1912,17 +1945,17 @@
         <v>46</v>
       </c>
       <c r="C51" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="D51" t="s">
         <v>112</v>
       </c>
       <c r="E51" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C51,'Feed rations'!$V$5:$V$17,0),MATCH(B51,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2.6881300304758931</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>41</v>
       </c>
@@ -1930,17 +1963,17 @@
         <v>46</v>
       </c>
       <c r="C52" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D52" t="s">
         <v>112</v>
       </c>
       <c r="E52" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C52,'Feed rations'!$V$5:$V$17,0),MATCH(B52,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+        <v>16.800812690474331</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>41</v>
       </c>
@@ -1948,17 +1981,17 @@
         <v>46</v>
       </c>
       <c r="C53" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="D53" t="s">
         <v>112</v>
       </c>
       <c r="E53" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C53,'Feed rations'!$V$5:$V$17,0),MATCH(B53,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>27.048006043083014</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3.920189627777344</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>41</v>
       </c>
@@ -1966,7 +1999,7 @@
         <v>46</v>
       </c>
       <c r="C54" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D54" t="s">
         <v>112</v>
@@ -1976,7 +2009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>41</v>
       </c>
@@ -1984,7 +2017,7 @@
         <v>46</v>
       </c>
       <c r="C55" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D55" t="s">
         <v>112</v>
@@ -1994,7 +2027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>41</v>
       </c>
@@ -2002,17 +2035,17 @@
         <v>46</v>
       </c>
       <c r="C56" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="D56" t="s">
         <v>112</v>
       </c>
       <c r="E56" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C56,'Feed rations'!$V$5:$V$17,0),MATCH(B56,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+        <v>27.048006043083014</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>41</v>
       </c>
@@ -2020,17 +2053,17 @@
         <v>46</v>
       </c>
       <c r="C57" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="D57" t="s">
         <v>112</v>
       </c>
       <c r="E57" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C57,'Feed rations'!$V$5:$V$17,0),MATCH(B57,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>5.8607486129561623</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>41</v>
       </c>
@@ -2038,7 +2071,7 @@
         <v>46</v>
       </c>
       <c r="C58" t="s">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="D58" t="s">
         <v>112</v>
@@ -2048,7 +2081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>41</v>
       </c>
@@ -2056,7 +2089,7 @@
         <v>46</v>
       </c>
       <c r="C59" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="D59" t="s">
         <v>112</v>
@@ -2066,61 +2099,61 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>41</v>
       </c>
       <c r="B60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C60" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D60" t="s">
         <v>112</v>
       </c>
       <c r="E60" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C60,'Feed rations'!$V$5:$V$17,0),MATCH(B60,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>52.05847593594973</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5.8607486129561623</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>41</v>
       </c>
       <c r="B61" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C61" t="s">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="D61" t="s">
         <v>112</v>
       </c>
       <c r="E61" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C61,'Feed rations'!$V$5:$V$17,0),MATCH(B61,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>1.3440650152379465</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>41</v>
       </c>
       <c r="B62" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C62" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D62" t="s">
         <v>112</v>
       </c>
       <c r="E62" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C62,'Feed rations'!$V$5:$V$17,0),MATCH(B62,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>12.963626223585813</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>41</v>
       </c>
@@ -2128,17 +2161,17 @@
         <v>47</v>
       </c>
       <c r="C63" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="D63" t="s">
         <v>112</v>
       </c>
       <c r="E63" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C63,'Feed rations'!$V$5:$V$17,0),MATCH(B63,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>1.960094813888672</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+        <v>52.05847593594973</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>41</v>
       </c>
@@ -2146,14 +2179,14 @@
         <v>47</v>
       </c>
       <c r="C64" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="D64" t="s">
         <v>112</v>
       </c>
       <c r="E64" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C64,'Feed rations'!$V$5:$V$17,0),MATCH(B64,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>1.3440650152379465</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -2164,14 +2197,14 @@
         <v>47</v>
       </c>
       <c r="C65" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D65" t="s">
         <v>112</v>
       </c>
       <c r="E65" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C65,'Feed rations'!$V$5:$V$17,0),MATCH(B65,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>12.963626223585813</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -2182,14 +2215,14 @@
         <v>47</v>
       </c>
       <c r="C66" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="D66" t="s">
         <v>112</v>
       </c>
       <c r="E66" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C66,'Feed rations'!$V$5:$V$17,0),MATCH(B66,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>24.343208405260931</v>
+        <v>1.960094813888672</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -2200,7 +2233,7 @@
         <v>47</v>
       </c>
       <c r="C67" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D67" t="s">
         <v>112</v>
@@ -2218,14 +2251,14 @@
         <v>47</v>
       </c>
       <c r="C68" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D68" t="s">
         <v>112</v>
       </c>
       <c r="E68" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C68,'Feed rations'!$V$5:$V$17,0),MATCH(B68,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>1.7471204866054095</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -2236,14 +2269,14 @@
         <v>47</v>
       </c>
       <c r="C69" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="D69" t="s">
         <v>112</v>
       </c>
       <c r="E69" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C69,'Feed rations'!$V$5:$V$17,0),MATCH(B69,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>24.343208405260931</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -2254,14 +2287,14 @@
         <v>47</v>
       </c>
       <c r="C70" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="D70" t="s">
         <v>112</v>
       </c>
       <c r="E70" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C70,'Feed rations'!$V$5:$V$17,0),MATCH(B70,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>5.5834091194714803</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -2272,14 +2305,14 @@
         <v>47</v>
       </c>
       <c r="C71" t="s">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="D71" t="s">
         <v>112</v>
       </c>
       <c r="E71" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C71,'Feed rations'!$V$5:$V$17,0),MATCH(B71,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>1.7471204866054095</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -2290,7 +2323,7 @@
         <v>47</v>
       </c>
       <c r="C72" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="D72" t="s">
         <v>112</v>
@@ -2305,17 +2338,17 @@
         <v>41</v>
       </c>
       <c r="B73" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C73" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D73" t="s">
         <v>112</v>
       </c>
       <c r="E73" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C73,'Feed rations'!$V$5:$V$17,0),MATCH(B73,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>55.910178622144024</v>
+        <v>5.5834091194714803</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -2323,17 +2356,17 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C74" t="s">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="D74" t="s">
         <v>112</v>
       </c>
       <c r="E74" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C74,'Feed rations'!$V$5:$V$17,0),MATCH(B74,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>1.3475047658841042</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -2341,17 +2374,17 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C75" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D75" t="s">
         <v>112</v>
       </c>
       <c r="E75" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C75,'Feed rations'!$V$5:$V$17,0),MATCH(B75,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>9.5448254250124034</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -2362,14 +2395,14 @@
         <v>48</v>
       </c>
       <c r="C76" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="D76" t="s">
         <v>112</v>
       </c>
       <c r="E76" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C76,'Feed rations'!$V$5:$V$17,0),MATCH(B76,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>3.2003238189747476</v>
+        <v>55.910178622144024</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -2380,14 +2413,14 @@
         <v>48</v>
       </c>
       <c r="C77" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="D77" t="s">
         <v>112</v>
       </c>
       <c r="E77" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C77,'Feed rations'!$V$5:$V$17,0),MATCH(B77,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>1.3475047658841042</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -2398,14 +2431,14 @@
         <v>48</v>
       </c>
       <c r="C78" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D78" t="s">
         <v>112</v>
       </c>
       <c r="E78" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C78,'Feed rations'!$V$5:$V$17,0),MATCH(B78,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>9.5448254250124034</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -2416,14 +2449,14 @@
         <v>48</v>
       </c>
       <c r="C79" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="D79" t="s">
         <v>112</v>
       </c>
       <c r="E79" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C79,'Feed rations'!$V$5:$V$17,0),MATCH(B79,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>21.742772443376154</v>
+        <v>3.2003238189747476</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -2434,7 +2467,7 @@
         <v>48</v>
       </c>
       <c r="C80" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D80" t="s">
         <v>112</v>
@@ -2452,14 +2485,14 @@
         <v>48</v>
       </c>
       <c r="C81" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D81" t="s">
         <v>112</v>
       </c>
       <c r="E81" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C81,'Feed rations'!$V$5:$V$17,0),MATCH(B81,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>1.3343217197924386</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -2470,14 +2503,14 @@
         <v>48</v>
       </c>
       <c r="C82" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="D82" t="s">
         <v>112</v>
       </c>
       <c r="E82" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C82,'Feed rations'!$V$5:$V$17,0),MATCH(B82,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>1.3788420860209438</v>
+        <v>21.742772443376154</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -2488,14 +2521,14 @@
         <v>48</v>
       </c>
       <c r="C83" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="D83" t="s">
         <v>112</v>
       </c>
       <c r="E83" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C83,'Feed rations'!$V$5:$V$17,0),MATCH(B83,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>5.5412311187951762</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -2506,14 +2539,14 @@
         <v>48</v>
       </c>
       <c r="C84" t="s">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="D84" t="s">
         <v>112</v>
       </c>
       <c r="E84" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C84,'Feed rations'!$V$5:$V$17,0),MATCH(B84,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>1.3343217197924386</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -2524,14 +2557,14 @@
         <v>48</v>
       </c>
       <c r="C85" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="D85" t="s">
         <v>112</v>
       </c>
       <c r="E85" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C85,'Feed rations'!$V$5:$V$17,0),MATCH(B85,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>1.3788420860209438</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -2539,17 +2572,17 @@
         <v>41</v>
       </c>
       <c r="B86" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C86" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D86" t="s">
         <v>112</v>
       </c>
       <c r="E86" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C86,'Feed rations'!$V$5:$V$17,0),MATCH(B86,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>58.797927209288808</v>
+        <v>5.5412311187951762</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -2557,17 +2590,17 @@
         <v>41</v>
       </c>
       <c r="B87" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C87" t="s">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="D87" t="s">
         <v>112</v>
       </c>
       <c r="E87" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C87,'Feed rations'!$V$5:$V$17,0),MATCH(B87,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>1.3523075713499491</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -2575,17 +2608,17 @@
         <v>41</v>
       </c>
       <c r="B88" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C88" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D88" t="s">
         <v>112</v>
       </c>
       <c r="E88" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C88,'Feed rations'!$V$5:$V$17,0),MATCH(B88,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>8.4519223209371823</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -2596,14 +2629,14 @@
         <v>49</v>
       </c>
       <c r="C89" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="D89" t="s">
         <v>112</v>
       </c>
       <c r="E89" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C89,'Feed rations'!$V$5:$V$17,0),MATCH(B89,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>2.1974998034436672</v>
+        <v>58.797927209288808</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -2614,14 +2647,14 @@
         <v>49</v>
       </c>
       <c r="C90" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="D90" t="s">
         <v>112</v>
       </c>
       <c r="E90" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C90,'Feed rations'!$V$5:$V$17,0),MATCH(B90,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>1.3523075713499491</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -2632,14 +2665,14 @@
         <v>49</v>
       </c>
       <c r="C91" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D91" t="s">
         <v>112</v>
       </c>
       <c r="E91" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C91,'Feed rations'!$V$5:$V$17,0),MATCH(B91,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>8.4519223209371823</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -2650,14 +2683,14 @@
         <v>49</v>
       </c>
       <c r="C92" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="D92" t="s">
         <v>112</v>
       </c>
       <c r="E92" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C92,'Feed rations'!$V$5:$V$17,0),MATCH(B92,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>19.824838165705017</v>
+        <v>2.1974998034436672</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -2668,7 +2701,7 @@
         <v>49</v>
       </c>
       <c r="C93" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D93" t="s">
         <v>112</v>
@@ -2686,14 +2719,14 @@
         <v>49</v>
       </c>
       <c r="C94" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D94" t="s">
         <v>112</v>
       </c>
       <c r="E94" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C94,'Feed rations'!$V$5:$V$17,0),MATCH(B94,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>1.3343217197924386</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -2704,14 +2737,14 @@
         <v>49</v>
       </c>
       <c r="C95" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="D95" t="s">
         <v>112</v>
       </c>
       <c r="E95" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C95,'Feed rations'!$V$5:$V$17,0),MATCH(B95,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>2.8828262179940776</v>
+        <v>19.824838165705017</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -2722,14 +2755,14 @@
         <v>49</v>
       </c>
       <c r="C96" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="D96" t="s">
         <v>112</v>
       </c>
       <c r="E96" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C96,'Feed rations'!$V$5:$V$17,0),MATCH(B96,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>5.1583569914888532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -2740,14 +2773,14 @@
         <v>49</v>
       </c>
       <c r="C97" t="s">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="D97" t="s">
         <v>112</v>
       </c>
       <c r="E97" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C97,'Feed rations'!$V$5:$V$17,0),MATCH(B97,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>1.3343217197924386</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -2758,14 +2791,14 @@
         <v>49</v>
       </c>
       <c r="C98" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="D98" t="s">
         <v>112</v>
       </c>
       <c r="E98" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C98,'Feed rations'!$V$5:$V$17,0),MATCH(B98,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>2.8828262179940776</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -2773,17 +2806,17 @@
         <v>41</v>
       </c>
       <c r="B99" t="s">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="C99" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D99" t="s">
         <v>112</v>
       </c>
       <c r="E99" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C99,'Feed rations'!$V$5:$V$17,0),MATCH(B99,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>58.797927209288808</v>
+        <v>5.1583569914888532</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -2791,17 +2824,17 @@
         <v>41</v>
       </c>
       <c r="B100" t="s">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="C100" t="s">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="D100" t="s">
         <v>112</v>
       </c>
       <c r="E100" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C100,'Feed rations'!$V$5:$V$17,0),MATCH(B100,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>1.3523075713499491</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -2809,17 +2842,17 @@
         <v>41</v>
       </c>
       <c r="B101" t="s">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="C101" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D101" t="s">
         <v>112</v>
       </c>
       <c r="E101" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C101,'Feed rations'!$V$5:$V$17,0),MATCH(B101,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>8.4519223209371823</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -2830,14 +2863,14 @@
         <v>89</v>
       </c>
       <c r="C102" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="D102" t="s">
         <v>112</v>
       </c>
       <c r="E102" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C102,'Feed rations'!$V$5:$V$17,0),MATCH(B102,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>2.1974998034436672</v>
+        <v>58.797927209288808</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -2848,14 +2881,14 @@
         <v>89</v>
       </c>
       <c r="C103" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="D103" t="s">
         <v>112</v>
       </c>
       <c r="E103" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C103,'Feed rations'!$V$5:$V$17,0),MATCH(B103,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>1.3523075713499491</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -2866,14 +2899,14 @@
         <v>89</v>
       </c>
       <c r="C104" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D104" t="s">
         <v>112</v>
       </c>
       <c r="E104" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C104,'Feed rations'!$V$5:$V$17,0),MATCH(B104,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>8.4519223209371823</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -2884,14 +2917,14 @@
         <v>89</v>
       </c>
       <c r="C105" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="D105" t="s">
         <v>112</v>
       </c>
       <c r="E105" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C105,'Feed rations'!$V$5:$V$17,0),MATCH(B105,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>19.824838165705017</v>
+        <v>2.1974998034436672</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -2902,7 +2935,7 @@
         <v>89</v>
       </c>
       <c r="C106" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D106" t="s">
         <v>112</v>
@@ -2920,14 +2953,14 @@
         <v>89</v>
       </c>
       <c r="C107" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D107" t="s">
         <v>112</v>
       </c>
       <c r="E107" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C107,'Feed rations'!$V$5:$V$17,0),MATCH(B107,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>1.3343217197924386</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -2938,14 +2971,14 @@
         <v>89</v>
       </c>
       <c r="C108" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="D108" t="s">
         <v>112</v>
       </c>
       <c r="E108" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C108,'Feed rations'!$V$5:$V$17,0),MATCH(B108,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>2.8828262179940776</v>
+        <v>19.824838165705017</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -2956,14 +2989,14 @@
         <v>89</v>
       </c>
       <c r="C109" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="D109" t="s">
         <v>112</v>
       </c>
       <c r="E109" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C109,'Feed rations'!$V$5:$V$17,0),MATCH(B109,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>5.1583569914888532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
@@ -2974,14 +3007,14 @@
         <v>89</v>
       </c>
       <c r="C110" t="s">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="D110" t="s">
         <v>112</v>
       </c>
       <c r="E110" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C110,'Feed rations'!$V$5:$V$17,0),MATCH(B110,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>1.3343217197924386</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
@@ -2992,72 +3025,72 @@
         <v>89</v>
       </c>
       <c r="C111" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="D111" t="s">
         <v>112</v>
       </c>
       <c r="E111" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C111,'Feed rations'!$V$5:$V$17,0),MATCH(B111,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>2.8828262179940776</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E112" s="4"/>
+      <c r="A112" t="s">
+        <v>41</v>
+      </c>
+      <c r="B112" t="s">
+        <v>89</v>
+      </c>
+      <c r="C112" t="s">
+        <v>23</v>
+      </c>
+      <c r="D112" t="s">
+        <v>112</v>
+      </c>
+      <c r="E112" s="4">
+        <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C112,'Feed rations'!$V$5:$V$17,0),MATCH(B112,'Feed rations'!$W$4:$AA$4,0))</f>
+        <v>5.1583569914888532</v>
+      </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B113" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="C113" t="s">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="D113" t="s">
         <v>112</v>
       </c>
       <c r="E113" s="4">
-        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C113,'Feed rations'!$V$5:$V$17,0),MATCH(B113,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>43.682112995233247</v>
+        <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C113,'Feed rations'!$V$5:$V$17,0),MATCH(B113,'Feed rations'!$W$4:$AA$4,0))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B114" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="C114" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D114" t="s">
         <v>112</v>
       </c>
       <c r="E114" s="4">
-        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C114,'Feed rations'!$V$5:$V$17,0),MATCH(B114,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>2.6881300304758931</v>
+        <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C114,'Feed rations'!$V$5:$V$17,0),MATCH(B114,'Feed rations'!$W$4:$AA$4,0))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>42</v>
-      </c>
-      <c r="B115" t="s">
-        <v>46</v>
-      </c>
-      <c r="C115" t="s">
-        <v>18</v>
-      </c>
-      <c r="D115" t="s">
-        <v>112</v>
-      </c>
-      <c r="E115" s="4">
-        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C115,'Feed rations'!$V$5:$V$17,0),MATCH(B115,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>16.800812690474331</v>
-      </c>
+      <c r="E115" s="4"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
@@ -3067,14 +3100,14 @@
         <v>46</v>
       </c>
       <c r="C116" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="D116" t="s">
         <v>112</v>
       </c>
       <c r="E116" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C116,'Feed rations'!$V$5:$V$17,0),MATCH(B116,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>3.920189627777344</v>
+        <v>43.682112995233247</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
@@ -3085,14 +3118,14 @@
         <v>46</v>
       </c>
       <c r="C117" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="D117" t="s">
         <v>112</v>
       </c>
       <c r="E117" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C117,'Feed rations'!$V$5:$V$17,0),MATCH(B117,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <v>2.6881300304758931</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -3103,14 +3136,14 @@
         <v>46</v>
       </c>
       <c r="C118" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D118" t="s">
         <v>112</v>
       </c>
       <c r="E118" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C118,'Feed rations'!$V$5:$V$17,0),MATCH(B118,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <v>16.800812690474331</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
@@ -3121,14 +3154,14 @@
         <v>46</v>
       </c>
       <c r="C119" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="D119" t="s">
         <v>112</v>
       </c>
       <c r="E119" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C119,'Feed rations'!$V$5:$V$17,0),MATCH(B119,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>27.048006043083014</v>
+        <v>3.920189627777344</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
@@ -3139,7 +3172,7 @@
         <v>46</v>
       </c>
       <c r="C120" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D120" t="s">
         <v>112</v>
@@ -3156,21 +3189,15 @@
       <c r="B121" t="s">
         <v>46</v>
       </c>
-      <c r="C121" s="87" t="s">
-        <v>130</v>
+      <c r="C121" t="s">
+        <v>20</v>
       </c>
       <c r="D121" t="s">
         <v>112</v>
       </c>
       <c r="E121" s="4">
-        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(H121,'Feed rations'!$V$5:$V$17,0),MATCH(B121,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
-      </c>
-      <c r="G121" s="87" t="s">
-        <v>131</v>
-      </c>
-      <c r="H121" t="s">
-        <v>22</v>
+        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C121,'Feed rations'!$V$5:$V$17,0),MATCH(B121,'Feed rations'!$AB$4:$AF$4,0))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
@@ -3181,14 +3208,14 @@
         <v>46</v>
       </c>
       <c r="C122" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="D122" t="s">
         <v>112</v>
       </c>
       <c r="E122" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C122,'Feed rations'!$V$5:$V$17,0),MATCH(B122,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <v>27.048006043083014</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
@@ -3199,14 +3226,14 @@
         <v>46</v>
       </c>
       <c r="C123" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="D123" t="s">
         <v>112</v>
       </c>
       <c r="E123" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C123,'Feed rations'!$V$5:$V$17,0),MATCH(B123,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>5.8607486129561623</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -3216,15 +3243,21 @@
       <c r="B124" t="s">
         <v>46</v>
       </c>
-      <c r="C124" t="s">
-        <v>92</v>
+      <c r="C124" s="87" t="s">
+        <v>128</v>
       </c>
       <c r="D124" t="s">
         <v>112</v>
       </c>
       <c r="E124" s="4">
-        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C124,'Feed rations'!$V$5:$V$17,0),MATCH(B124,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(H124,'Feed rations'!$V$5:$V$17,0),MATCH(B124,'Feed rations'!$AB$4:$AF$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="G124" s="87" t="s">
+        <v>129</v>
+      </c>
+      <c r="H124" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
@@ -3235,7 +3268,7 @@
         <v>46</v>
       </c>
       <c r="C125" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="D125" t="s">
         <v>112</v>
@@ -3250,17 +3283,17 @@
         <v>42</v>
       </c>
       <c r="B126" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C126" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D126" t="s">
         <v>112</v>
       </c>
       <c r="E126" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C126,'Feed rations'!$V$5:$V$17,0),MATCH(B126,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>58.016195973989106</v>
+        <v>5.8607486129561623</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
@@ -3268,10 +3301,10 @@
         <v>42</v>
       </c>
       <c r="B127" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C127" t="s">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="D127" t="s">
         <v>112</v>
@@ -3286,17 +3319,17 @@
         <v>42</v>
       </c>
       <c r="B128" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C128" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D128" t="s">
         <v>112</v>
       </c>
       <c r="E128" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C128,'Feed rations'!$V$5:$V$17,0),MATCH(B128,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>13.254201084237993</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -3307,14 +3340,14 @@
         <v>47</v>
       </c>
       <c r="C129" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="D129" t="s">
         <v>112</v>
       </c>
       <c r="E129" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C129,'Feed rations'!$V$5:$V$17,0),MATCH(B129,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>5.1156565588286975</v>
+        <v>58.016195973989106</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
@@ -3325,14 +3358,14 @@
         <v>47</v>
       </c>
       <c r="C130" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="D130" t="s">
         <v>112</v>
       </c>
       <c r="E130" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C130,'Feed rations'!$V$5:$V$17,0),MATCH(B130,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>8.2737362949343645</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -3343,14 +3376,14 @@
         <v>47</v>
       </c>
       <c r="C131" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D131" t="s">
         <v>112</v>
       </c>
       <c r="E131" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C131,'Feed rations'!$V$5:$V$17,0),MATCH(B131,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>3.6907353080344469</v>
+        <v>13.254201084237993</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
@@ -3361,14 +3394,14 @@
         <v>47</v>
       </c>
       <c r="C132" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="D132" t="s">
         <v>112</v>
       </c>
       <c r="E132" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C132,'Feed rations'!$V$5:$V$17,0),MATCH(B132,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <v>5.1156565588286975</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
@@ -3379,14 +3412,14 @@
         <v>47</v>
       </c>
       <c r="C133" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D133" t="s">
         <v>112</v>
       </c>
       <c r="E133" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C133,'Feed rations'!$V$5:$V$17,0),MATCH(B133,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>2.3523367897362411</v>
+        <v>8.2737362949343645</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
@@ -3396,21 +3429,15 @@
       <c r="B134" t="s">
         <v>47</v>
       </c>
-      <c r="C134" s="87" t="s">
-        <v>130</v>
+      <c r="C134" t="s">
+        <v>20</v>
       </c>
       <c r="D134" t="s">
         <v>112</v>
       </c>
       <c r="E134" s="4">
-        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(H134,'Feed rations'!$V$5:$V$17,0),MATCH(B134,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>1.5817437034433346</v>
-      </c>
-      <c r="G134" s="87" t="s">
-        <v>131</v>
-      </c>
-      <c r="H134" t="s">
-        <v>22</v>
+        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C134,'Feed rations'!$V$5:$V$17,0),MATCH(B134,'Feed rations'!$AB$4:$AF$4,0))</f>
+        <v>3.6907353080344469</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
@@ -3421,7 +3448,7 @@
         <v>47</v>
       </c>
       <c r="C135" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="D135" t="s">
         <v>112</v>
@@ -3439,14 +3466,14 @@
         <v>47</v>
       </c>
       <c r="C136" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="D136" t="s">
         <v>112</v>
       </c>
       <c r="E136" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C136,'Feed rations'!$V$5:$V$17,0),MATCH(B136,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <v>2.3523367897362411</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
@@ -3456,15 +3483,21 @@
       <c r="B137" t="s">
         <v>47</v>
       </c>
-      <c r="C137" t="s">
-        <v>92</v>
+      <c r="C137" s="87" t="s">
+        <v>128</v>
       </c>
       <c r="D137" t="s">
         <v>112</v>
       </c>
       <c r="E137" s="4">
-        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C137,'Feed rations'!$V$5:$V$17,0),MATCH(B137,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>6.1512255133907452</v>
+        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(H137,'Feed rations'!$V$5:$V$17,0),MATCH(B137,'Feed rations'!$AB$4:$AF$4,0))</f>
+        <v>1.5817437034433346</v>
+      </c>
+      <c r="G137" s="87" t="s">
+        <v>129</v>
+      </c>
+      <c r="H137" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
@@ -3475,14 +3508,14 @@
         <v>47</v>
       </c>
       <c r="C138" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="D138" t="s">
         <v>112</v>
       </c>
       <c r="E138" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C138,'Feed rations'!$V$5:$V$17,0),MATCH(B138,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>1.5641687734050753</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -3490,17 +3523,17 @@
         <v>42</v>
       </c>
       <c r="B139" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C139" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D139" t="s">
         <v>112</v>
       </c>
       <c r="E139" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C139,'Feed rations'!$V$5:$V$17,0),MATCH(B139,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>57.806020490924027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
@@ -3508,17 +3541,17 @@
         <v>42</v>
       </c>
       <c r="B140" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C140" t="s">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="D140" t="s">
         <v>112</v>
       </c>
       <c r="E140" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C140,'Feed rations'!$V$5:$V$17,0),MATCH(B140,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <v>6.1512255133907452</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
@@ -3526,17 +3559,17 @@
         <v>42</v>
       </c>
       <c r="B141" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C141" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D141" t="s">
         <v>112</v>
       </c>
       <c r="E141" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C141,'Feed rations'!$V$5:$V$17,0),MATCH(B141,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>14.91384967080074</v>
+        <v>1.5641687734050753</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -3547,14 +3580,14 @@
         <v>48</v>
       </c>
       <c r="C142" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="D142" t="s">
         <v>112</v>
       </c>
       <c r="E142" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C142,'Feed rations'!$V$5:$V$17,0),MATCH(B142,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>8.3761840506164251</v>
+        <v>57.806020490924027</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -3565,14 +3598,14 @@
         <v>48</v>
       </c>
       <c r="C143" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="D143" t="s">
         <v>112</v>
       </c>
       <c r="E143" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C143,'Feed rations'!$V$5:$V$17,0),MATCH(B143,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>4.1368681474671822</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -3583,14 +3616,14 @@
         <v>48</v>
       </c>
       <c r="C144" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D144" t="s">
         <v>112</v>
       </c>
       <c r="E144" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C144,'Feed rations'!$V$5:$V$17,0),MATCH(B144,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>4.021954820011894</v>
+        <v>14.91384967080074</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
@@ -3601,14 +3634,14 @@
         <v>48</v>
       </c>
       <c r="C145" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="D145" t="s">
         <v>112</v>
       </c>
       <c r="E145" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C145,'Feed rations'!$V$5:$V$17,0),MATCH(B145,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <v>8.3761840506164251</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
@@ -3619,39 +3652,32 @@
         <v>48</v>
       </c>
       <c r="C146" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D146" t="s">
         <v>112</v>
       </c>
       <c r="E146" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C146,'Feed rations'!$V$5:$V$17,0),MATCH(B146,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>2.3652615404978614</v>
+        <v>4.1368681474671822</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A147" s="79" t="s">
-        <v>42</v>
-      </c>
-      <c r="B147" s="79" t="s">
+      <c r="A147" t="s">
+        <v>42</v>
+      </c>
+      <c r="B147" t="s">
         <v>48</v>
       </c>
-      <c r="C147" s="87" t="s">
-        <v>130</v>
-      </c>
-      <c r="D147" s="79" t="s">
-        <v>112</v>
-      </c>
-      <c r="E147" s="78">
-        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(H147,'Feed rations'!$V$5:$V$17,0),MATCH(B147,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0.7908718517216673</v>
-      </c>
-      <c r="F147" s="87"/>
-      <c r="G147" s="87" t="s">
-        <v>131</v>
-      </c>
-      <c r="H147" t="s">
-        <v>22</v>
+      <c r="C147" t="s">
+        <v>20</v>
+      </c>
+      <c r="D147" t="s">
+        <v>112</v>
+      </c>
+      <c r="E147" s="4">
+        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C147,'Feed rations'!$V$5:$V$17,0),MATCH(B147,'Feed rations'!$AB$4:$AF$4,0))</f>
+        <v>4.021954820011894</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
@@ -3662,7 +3688,7 @@
         <v>48</v>
       </c>
       <c r="C148" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="D148" t="s">
         <v>112</v>
@@ -3680,32 +3706,39 @@
         <v>48</v>
       </c>
       <c r="C149" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="D149" t="s">
         <v>112</v>
       </c>
       <c r="E149" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C149,'Feed rations'!$V$5:$V$17,0),MATCH(B149,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <v>2.3652615404978614</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>42</v>
-      </c>
-      <c r="B150" t="s">
+      <c r="A150" s="79" t="s">
+        <v>42</v>
+      </c>
+      <c r="B150" s="79" t="s">
         <v>48</v>
       </c>
-      <c r="C150" t="s">
-        <v>92</v>
-      </c>
-      <c r="D150" t="s">
-        <v>112</v>
-      </c>
-      <c r="E150" s="4">
-        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C150,'Feed rations'!$V$5:$V$17,0),MATCH(B150,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>6.8069050412576626</v>
+      <c r="C150" s="87" t="s">
+        <v>128</v>
+      </c>
+      <c r="D150" s="79" t="s">
+        <v>112</v>
+      </c>
+      <c r="E150" s="78">
+        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(H150,'Feed rations'!$V$5:$V$17,0),MATCH(B150,'Feed rations'!$AB$4:$AF$4,0))</f>
+        <v>0.7908718517216673</v>
+      </c>
+      <c r="F150" s="87"/>
+      <c r="G150" s="87" t="s">
+        <v>129</v>
+      </c>
+      <c r="H150" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
@@ -3716,14 +3749,14 @@
         <v>48</v>
       </c>
       <c r="C151" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="D151" t="s">
         <v>112</v>
       </c>
       <c r="E151" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C151,'Feed rations'!$V$5:$V$17,0),MATCH(B151,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0.78208438670253766</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
@@ -3731,17 +3764,17 @@
         <v>42</v>
       </c>
       <c r="B152" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C152" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D152" t="s">
         <v>112</v>
       </c>
       <c r="E152" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C152,'Feed rations'!$V$5:$V$17,0),MATCH(B152,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>57.595845007858948</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
@@ -3749,17 +3782,17 @@
         <v>42</v>
       </c>
       <c r="B153" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C153" t="s">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="D153" t="s">
         <v>112</v>
       </c>
       <c r="E153" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C153,'Feed rations'!$V$5:$V$17,0),MATCH(B153,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <v>6.8069050412576626</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
@@ -3767,17 +3800,17 @@
         <v>42</v>
       </c>
       <c r="B154" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C154" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D154" t="s">
         <v>112</v>
       </c>
       <c r="E154" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C154,'Feed rations'!$V$5:$V$17,0),MATCH(B154,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>16.573498257363489</v>
+        <v>0.78208438670253766</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
@@ -3788,14 +3821,14 @@
         <v>49</v>
       </c>
       <c r="C155" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="D155" t="s">
         <v>112</v>
       </c>
       <c r="E155" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C155,'Feed rations'!$V$5:$V$17,0),MATCH(B155,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>11.636711542404154</v>
+        <v>57.595845007858948</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
@@ -3806,7 +3839,7 @@
         <v>49</v>
       </c>
       <c r="C156" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="D156" t="s">
         <v>112</v>
@@ -3824,14 +3857,14 @@
         <v>49</v>
       </c>
       <c r="C157" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D157" t="s">
         <v>112</v>
       </c>
       <c r="E157" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C157,'Feed rations'!$V$5:$V$17,0),MATCH(B157,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>4.3531743319893401</v>
+        <v>16.573498257363489</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
@@ -3842,14 +3875,14 @@
         <v>49</v>
       </c>
       <c r="C158" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="D158" t="s">
         <v>112</v>
       </c>
       <c r="E158" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C158,'Feed rations'!$V$5:$V$17,0),MATCH(B158,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <v>11.636711542404154</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -3860,14 +3893,14 @@
         <v>49</v>
       </c>
       <c r="C159" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D159" t="s">
         <v>112</v>
       </c>
       <c r="E159" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C159,'Feed rations'!$V$5:$V$17,0),MATCH(B159,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>2.3781862912594818</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -3877,21 +3910,15 @@
       <c r="B160" t="s">
         <v>49</v>
       </c>
-      <c r="C160" s="87" t="s">
-        <v>130</v>
+      <c r="C160" t="s">
+        <v>20</v>
       </c>
       <c r="D160" t="s">
         <v>112</v>
       </c>
       <c r="E160" s="4">
-        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(H160,'Feed rations'!$V$5:$V$17,0),MATCH(B160,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
-      </c>
-      <c r="G160" s="87" t="s">
-        <v>131</v>
-      </c>
-      <c r="H160" t="s">
-        <v>22</v>
+        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C160,'Feed rations'!$V$5:$V$17,0),MATCH(B160,'Feed rations'!$AB$4:$AF$4,0))</f>
+        <v>4.3531743319893401</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
@@ -3902,7 +3929,7 @@
         <v>49</v>
       </c>
       <c r="C161" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="D161" t="s">
         <v>112</v>
@@ -3920,14 +3947,14 @@
         <v>49</v>
       </c>
       <c r="C162" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="D162" t="s">
         <v>112</v>
       </c>
       <c r="E162" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C162,'Feed rations'!$V$5:$V$17,0),MATCH(B162,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <v>2.3781862912594818</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -3937,15 +3964,21 @@
       <c r="B163" t="s">
         <v>49</v>
       </c>
-      <c r="C163" t="s">
-        <v>92</v>
+      <c r="C163" s="87" t="s">
+        <v>128</v>
       </c>
       <c r="D163" t="s">
         <v>112</v>
       </c>
       <c r="E163" s="4">
-        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C163,'Feed rations'!$V$5:$V$17,0),MATCH(B163,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>7.4625845691245809</v>
+        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(H163,'Feed rations'!$V$5:$V$17,0),MATCH(B163,'Feed rations'!$AB$4:$AF$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="G163" s="87" t="s">
+        <v>129</v>
+      </c>
+      <c r="H163" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
@@ -3956,7 +3989,7 @@
         <v>49</v>
       </c>
       <c r="C164" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="D164" t="s">
         <v>112</v>
@@ -3971,17 +4004,17 @@
         <v>42</v>
       </c>
       <c r="B165" t="s">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="C165" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D165" t="s">
         <v>112</v>
       </c>
       <c r="E165" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C165,'Feed rations'!$V$5:$V$17,0),MATCH(B165,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>57.595845007858948</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -3989,17 +4022,17 @@
         <v>42</v>
       </c>
       <c r="B166" t="s">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="C166" t="s">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="D166" t="s">
         <v>112</v>
       </c>
       <c r="E166" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C166,'Feed rations'!$V$5:$V$17,0),MATCH(B166,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <v>7.4625845691245809</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
@@ -4007,17 +4040,17 @@
         <v>42</v>
       </c>
       <c r="B167" t="s">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="C167" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D167" t="s">
         <v>112</v>
       </c>
       <c r="E167" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C167,'Feed rations'!$V$5:$V$17,0),MATCH(B167,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>16.573498257363489</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
@@ -4028,14 +4061,14 @@
         <v>89</v>
       </c>
       <c r="C168" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="D168" t="s">
         <v>112</v>
       </c>
       <c r="E168" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C168,'Feed rations'!$V$5:$V$17,0),MATCH(B168,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>11.636711542404154</v>
+        <v>57.595845007858948</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
@@ -4046,7 +4079,7 @@
         <v>89</v>
       </c>
       <c r="C169" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="D169" t="s">
         <v>112</v>
@@ -4064,14 +4097,14 @@
         <v>89</v>
       </c>
       <c r="C170" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D170" t="s">
         <v>112</v>
       </c>
       <c r="E170" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C170,'Feed rations'!$V$5:$V$17,0),MATCH(B170,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>4.3531743319893401</v>
+        <v>16.573498257363489</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
@@ -4082,14 +4115,14 @@
         <v>89</v>
       </c>
       <c r="C171" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="D171" t="s">
         <v>112</v>
       </c>
       <c r="E171" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C171,'Feed rations'!$V$5:$V$17,0),MATCH(B171,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <v>11.636711542404154</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
@@ -4100,14 +4133,14 @@
         <v>89</v>
       </c>
       <c r="C172" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D172" t="s">
         <v>112</v>
       </c>
       <c r="E172" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C172,'Feed rations'!$V$5:$V$17,0),MATCH(B172,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>2.3781862912594818</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
@@ -4117,21 +4150,15 @@
       <c r="B173" t="s">
         <v>89</v>
       </c>
-      <c r="C173" s="87" t="s">
-        <v>130</v>
+      <c r="C173" t="s">
+        <v>20</v>
       </c>
       <c r="D173" t="s">
         <v>112</v>
       </c>
       <c r="E173" s="4">
-        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(H173,'Feed rations'!$V$5:$V$17,0),MATCH(B173,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
-      </c>
-      <c r="G173" s="87" t="s">
-        <v>131</v>
-      </c>
-      <c r="H173" t="s">
-        <v>22</v>
+        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C173,'Feed rations'!$V$5:$V$17,0),MATCH(B173,'Feed rations'!$AB$4:$AF$4,0))</f>
+        <v>4.3531743319893401</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
@@ -4142,7 +4169,7 @@
         <v>89</v>
       </c>
       <c r="C174" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="D174" t="s">
         <v>112</v>
@@ -4160,14 +4187,14 @@
         <v>89</v>
       </c>
       <c r="C175" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="D175" t="s">
         <v>112</v>
       </c>
       <c r="E175" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C175,'Feed rations'!$V$5:$V$17,0),MATCH(B175,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <v>2.3781862912594818</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
@@ -4177,15 +4204,21 @@
       <c r="B176" t="s">
         <v>89</v>
       </c>
-      <c r="C176" t="s">
-        <v>92</v>
+      <c r="C176" s="87" t="s">
+        <v>128</v>
       </c>
       <c r="D176" t="s">
         <v>112</v>
       </c>
       <c r="E176" s="4">
-        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C176,'Feed rations'!$V$5:$V$17,0),MATCH(B176,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>7.4625845691245809</v>
+        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(H176,'Feed rations'!$V$5:$V$17,0),MATCH(B176,'Feed rations'!$AB$4:$AF$4,0))</f>
+        <v>0</v>
+      </c>
+      <c r="G176" s="87" t="s">
+        <v>129</v>
+      </c>
+      <c r="H176" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
@@ -4196,7 +4229,7 @@
         <v>89</v>
       </c>
       <c r="C177" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="D177" t="s">
         <v>112</v>
@@ -4206,9 +4239,66 @@
         <v>0</v>
       </c>
     </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>42</v>
+      </c>
+      <c r="B178" t="s">
+        <v>89</v>
+      </c>
+      <c r="C178" t="s">
+        <v>23</v>
+      </c>
+      <c r="D178" t="s">
+        <v>112</v>
+      </c>
+      <c r="E178" s="4">
+        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C178,'Feed rations'!$V$5:$V$17,0),MATCH(B178,'Feed rations'!$AB$4:$AF$4,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>42</v>
+      </c>
+      <c r="B179" t="s">
+        <v>89</v>
+      </c>
+      <c r="C179" t="s">
+        <v>92</v>
+      </c>
+      <c r="D179" t="s">
+        <v>112</v>
+      </c>
+      <c r="E179" s="4">
+        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C179,'Feed rations'!$V$5:$V$17,0),MATCH(B179,'Feed rations'!$AB$4:$AF$4,0))</f>
+        <v>7.4625845691245809</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>42</v>
+      </c>
+      <c r="B180" t="s">
+        <v>89</v>
+      </c>
+      <c r="C180" t="s">
+        <v>27</v>
+      </c>
+      <c r="D180" t="s">
+        <v>112</v>
+      </c>
+      <c r="E180" s="4">
+        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C180,'Feed rations'!$V$5:$V$17,0),MATCH(B180,'Feed rations'!$AB$4:$AF$4,0))</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H29" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -4249,14 +4339,14 @@
         <v>67</v>
       </c>
       <c r="F2" s="52" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G2" s="53"/>
       <c r="H2" s="53"/>
       <c r="I2" s="53"/>
       <c r="J2" s="53"/>
       <c r="K2" s="62" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L2" s="55"/>
       <c r="M2" s="21"/>
@@ -6282,12 +6372,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
